--- a/data/states/ri/raw_download.xlsx
+++ b/data/states/ri/raw_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rigov.sharepoint.com/sites/DLT-WDS-Administrative-WARNNotice_RapidResponse/Shared Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E43C28B4-3908-4176-A9E5-61C99C5CA500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E342F12-17AB-423F-9CD4-68EB2C988EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="212">
   <si>
     <t>Rhode Island WARN Report</t>
   </si>
@@ -71,6 +71,47 @@
     <t>Union Address</t>
   </si>
   <si>
+    <t xml:space="preserve">Hasbro, Inc. </t>
+  </si>
+  <si>
+    <t>Pawtucket, RI</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Up to 587 - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Relocation offered</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yes - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HQ Relocating</t>
+    </r>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t xml:space="preserve">Conduent </t>
   </si>
   <si>
@@ -89,9 +130,6 @@
     <t xml:space="preserve"> 9,891 Remote Workers (2 from RI)</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Allied Group, LLC</t>
   </si>
   <si>
@@ -105,9 +143,6 @@
   </si>
   <si>
     <t>Northeast Transportation Services LLC</t>
-  </si>
-  <si>
-    <t>Pawtucket, RI</t>
   </si>
   <si>
     <t>Teamsters Local 251, 121 Brightridge Avenue, East Providence, RI 02914</t>
@@ -672,7 +707,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -769,6 +804,14 @@
     <font>
       <b/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1349,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CB0631-2A55-452F-AC55-B4E9E0391533}">
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -1360,10 +1403,10 @@
     <col min="6" max="6" width="15.625" customWidth="1"/>
     <col min="7" max="7" width="20.25" customWidth="1"/>
     <col min="8" max="8" width="16.875" customWidth="1"/>
-    <col min="9" max="9" width="51.5" customWidth="1"/>
+    <col min="9" max="9" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:18" ht="15.6" customHeight="1">
       <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
@@ -1376,7 +1419,7 @@
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:18" ht="15.6" customHeight="1">
       <c r="A2" s="83"/>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -1387,7 +1430,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:19" ht="31.15">
+    <row r="3" spans="1:18" ht="30.95">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="48"/>
@@ -1396,9 +1439,9 @@
       <c r="F3" s="41"/>
       <c r="G3" s="82"/>
       <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-    </row>
-    <row r="4" spans="1:19" s="54" customFormat="1" ht="22.15" customHeight="1">
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:18" s="54" customFormat="1" ht="22.15" customHeight="1">
       <c r="A4" s="76" t="s">
         <v>1</v>
       </c>
@@ -1435,14 +1478,13 @@
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4"/>
-      <c r="S4"/>
-    </row>
-    <row r="5" spans="1:19" ht="16.5">
+    </row>
+    <row r="5" spans="1:18" ht="30.95">
       <c r="A5" s="71">
-        <v>46199</v>
+        <v>46303</v>
       </c>
       <c r="B5" s="71">
-        <v>46202</v>
+        <v>46303</v>
       </c>
       <c r="C5" s="80" t="s">
         <v>10</v>
@@ -1454,76 +1496,65 @@
         <v>12</v>
       </c>
       <c r="F5" s="71">
+        <v>46380</v>
+      </c>
+      <c r="G5" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="79" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="71">
+        <v>46199</v>
+      </c>
+      <c r="B6" s="71">
+        <v>46202</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="71">
         <v>46262</v>
       </c>
-      <c r="H5" s="79"/>
-    </row>
-    <row r="6" spans="1:19" ht="31.15">
-      <c r="A6" s="71">
+      <c r="H6" s="79"/>
+    </row>
+    <row r="7" spans="1:18" ht="30.95">
+      <c r="A7" s="71">
         <v>46143</v>
       </c>
-      <c r="B6" s="71">
+      <c r="B7" s="71">
         <v>46147</v>
       </c>
-      <c r="C6" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="71">
+      <c r="C7" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="71">
         <v>46204</v>
       </c>
-      <c r="H6" s="79" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" s="54" customFormat="1" ht="22.15" customHeight="1">
-      <c r="A7" s="71">
+      <c r="H7" s="79" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="54" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A8" s="71">
         <v>46107</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B8" s="71">
         <v>46112</v>
-      </c>
-      <c r="C7" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="79">
-        <v>154</v>
-      </c>
-      <c r="F7" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="79" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="72"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="73"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="73"/>
-    </row>
-    <row r="8" spans="1:19" s="74" customFormat="1" ht="31.15">
-      <c r="A8" s="71">
-        <v>46100</v>
-      </c>
-      <c r="B8" s="71">
-        <v>46100</v>
       </c>
       <c r="C8" s="72" t="s">
         <v>21</v>
@@ -1532,20 +1563,18 @@
         <v>22</v>
       </c>
       <c r="E8" s="79">
-        <v>52</v>
-      </c>
-      <c r="F8" s="71">
-        <v>46151</v>
+        <v>154</v>
+      </c>
+      <c r="F8" s="71" t="s">
+        <v>23</v>
       </c>
       <c r="G8" s="79" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H8" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="72" t="s">
-        <v>23</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="I8" s="72"/>
       <c r="J8" s="73"/>
       <c r="K8" s="73"/>
       <c r="L8" s="73"/>
@@ -1555,32 +1584,69 @@
       <c r="P8" s="73"/>
       <c r="Q8" s="73"/>
       <c r="R8" s="73"/>
-      <c r="S8" s="73"/>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="70">
+    </row>
+    <row r="9" spans="1:18" s="74" customFormat="1" ht="46.5">
+      <c r="A9" s="71">
+        <v>46100</v>
+      </c>
+      <c r="B9" s="71">
+        <v>46100</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="79">
+        <v>52</v>
+      </c>
+      <c r="F9" s="71">
+        <v>46151</v>
+      </c>
+      <c r="G9" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="70">
         <v>46035</v>
       </c>
-      <c r="B9" s="70">
+      <c r="B10" s="70">
         <v>46035</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="28">
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="28">
         <v>38</v>
       </c>
-      <c r="F9" s="70">
+      <c r="F10" s="70">
         <v>46096</v>
       </c>
-      <c r="G9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>16</v>
+      <c r="G10" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1588,6 +1654,7 @@
     <mergeCell ref="A1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1692,10 +1759,10 @@
         <v>45910</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E5" s="62">
         <v>2</v>
@@ -1704,10 +1771,10 @@
         <v>45975</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H5" s="63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I5" s="63"/>
       <c r="J5"/>
@@ -1729,10 +1796,10 @@
         <v>45903</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="62">
         <v>105</v>
@@ -1741,13 +1808,13 @@
         <v>45964</v>
       </c>
       <c r="G6" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I6" s="61" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -1760,7 +1827,7 @@
       <c r="R6"/>
       <c r="S6"/>
     </row>
-    <row r="7" spans="1:19" s="54" customFormat="1" ht="31.15">
+    <row r="7" spans="1:19" s="54" customFormat="1" ht="30.95">
       <c r="A7" s="63">
         <v>45814</v>
       </c>
@@ -1768,10 +1835,10 @@
         <v>45816</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" s="62">
         <v>125</v>
@@ -1780,10 +1847,10 @@
         <v>45874</v>
       </c>
       <c r="G7" s="62" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H7" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1805,10 +1872,10 @@
         <v>45736</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D8" s="61" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" s="62">
         <v>20</v>
@@ -1817,10 +1884,10 @@
         <v>45800</v>
       </c>
       <c r="G8" s="61" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H8" s="61" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1842,20 +1909,20 @@
         <v>45694</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="63"/>
       <c r="F9" s="63">
         <v>45815</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
@@ -1920,7 +1987,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:19" ht="31.15">
+    <row r="3" spans="1:19" ht="30.95">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="48"/>
@@ -1978,10 +2045,10 @@
         <v>45621</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E5" s="38">
         <v>796</v>
@@ -1990,10 +2057,10 @@
         <v>45682</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I5" s="38"/>
     </row>
@@ -2005,10 +2072,10 @@
         <v>45617</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="38" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>33</v>
       </c>
       <c r="E6" s="38">
         <v>121</v>
@@ -2017,10 +2084,10 @@
         <v>45681</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I6" s="39"/>
       <c r="J6" s="34"/>
@@ -2042,10 +2109,10 @@
         <v>45608</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" s="38">
         <v>136</v>
@@ -2054,13 +2121,13 @@
         <v>45726</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
@@ -2081,22 +2148,22 @@
         <v>45572</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E8" s="38">
         <v>632</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="34"/>
@@ -2118,10 +2185,10 @@
         <v>45567</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E9" s="38">
         <v>1</v>
@@ -2130,7 +2197,7 @@
         <v>45626</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
@@ -2143,20 +2210,20 @@
         <v>45560</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="38">
         <v>13</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I10" s="38"/>
     </row>
@@ -2168,20 +2235,20 @@
         <v>45526</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E11" s="38">
         <v>117</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I11" s="38"/>
     </row>
@@ -2193,10 +2260,10 @@
         <v>45504</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" s="38">
         <v>205</v>
@@ -2205,10 +2272,10 @@
         <v>45658</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I12" s="38"/>
     </row>
@@ -2220,10 +2287,10 @@
         <v>45485</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E13" s="38">
         <v>58</v>
@@ -2232,10 +2299,10 @@
         <v>45541</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I13" s="38"/>
     </row>
@@ -2247,10 +2314,10 @@
         <v>45432</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E14" s="38">
         <v>30</v>
@@ -2259,27 +2326,27 @@
         <v>45488</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B15" s="40">
         <v>45421</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E15" s="38">
         <v>1029</v>
@@ -2288,13 +2355,13 @@
         <v>45473</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2305,22 +2372,22 @@
         <v>45414</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E16" s="38">
         <v>36</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I16" s="38"/>
     </row>
@@ -2332,22 +2399,22 @@
         <v>45383</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F17" s="40">
         <v>45412</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I17" s="38"/>
     </row>
@@ -2359,10 +2426,10 @@
         <v>45383</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E18" s="38">
         <v>1</v>
@@ -2371,10 +2438,10 @@
         <v>45443</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I18" s="38"/>
     </row>
@@ -2386,10 +2453,10 @@
         <v>45349</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E19" s="38">
         <v>48</v>
@@ -2398,10 +2465,10 @@
         <v>45611</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I19" s="38"/>
     </row>
@@ -2413,10 +2480,10 @@
         <v>45328</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E20" s="38">
         <v>130</v>
@@ -2425,13 +2492,13 @@
         <v>45384</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2442,10 +2509,10 @@
         <v>45316</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E21" s="38">
         <v>1</v>
@@ -2454,21 +2521,21 @@
         <v>45316</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I21" s="40"/>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="15">
+    <row r="22" spans="1:9" s="6" customFormat="1">
       <c r="B22" s="11"/>
       <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="15"/>
       <c r="F22" s="42"/>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="15">
+    <row r="23" spans="1:9" s="6" customFormat="1">
       <c r="B23" s="11"/>
       <c r="C23" s="49"/>
       <c r="D23" s="12"/>
@@ -2482,7 +2549,7 @@
       <c r="E24" s="15"/>
       <c r="F24" s="42"/>
     </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="25" spans="1:9" s="5" customFormat="1">
       <c r="B25" s="11"/>
       <c r="C25" s="49"/>
       <c r="D25" s="12"/>
@@ -2492,7 +2559,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="26" spans="1:9" s="5" customFormat="1">
       <c r="B26" s="11"/>
       <c r="C26" s="49"/>
       <c r="D26" s="12"/>
@@ -2500,7 +2567,7 @@
       <c r="F26" s="42"/>
       <c r="I26" s="17"/>
     </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="27" spans="1:9" s="5" customFormat="1">
       <c r="B27" s="19"/>
       <c r="C27" s="36"/>
       <c r="D27" s="20"/>
@@ -2510,7 +2577,7 @@
       <c r="H27" s="21"/>
       <c r="I27" s="8"/>
     </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="28" spans="1:9" s="5" customFormat="1">
       <c r="A28" s="11"/>
       <c r="B28" s="19"/>
       <c r="C28" s="50"/>
@@ -2521,7 +2588,7 @@
       <c r="H28" s="22"/>
       <c r="I28" s="22"/>
     </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="29" spans="1:9" s="5" customFormat="1">
       <c r="A29" s="11"/>
       <c r="B29" s="19"/>
       <c r="C29" s="51"/>
@@ -2531,7 +2598,7 @@
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
     </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="30" spans="1:9" s="5" customFormat="1">
       <c r="A30" s="11"/>
       <c r="B30" s="19"/>
       <c r="C30" s="51"/>
@@ -2542,7 +2609,7 @@
       <c r="H30" s="24"/>
       <c r="I30" s="24"/>
     </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="31" spans="1:9" s="5" customFormat="1">
       <c r="A31" s="18"/>
       <c r="B31" s="19"/>
       <c r="C31" s="51"/>
@@ -2552,7 +2619,7 @@
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
     </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="32" spans="1:9" s="5" customFormat="1">
       <c r="A32" s="11"/>
       <c r="B32" s="19"/>
       <c r="C32" s="51"/>
@@ -2562,7 +2629,7 @@
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
     </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="33" spans="1:9" s="5" customFormat="1">
       <c r="A33" s="19"/>
       <c r="B33" s="19"/>
       <c r="C33" s="51"/>
@@ -2572,7 +2639,7 @@
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
     </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="34" spans="1:9" s="5" customFormat="1">
       <c r="A34" s="19"/>
       <c r="B34" s="19"/>
       <c r="C34" s="51"/>
@@ -2582,7 +2649,7 @@
       <c r="G34" s="24"/>
       <c r="H34" s="24"/>
     </row>
-    <row r="35" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="35" spans="1:9" s="5" customFormat="1">
       <c r="A35" s="19"/>
       <c r="B35" s="19"/>
       <c r="C35" s="51"/>
@@ -2593,7 +2660,7 @@
       <c r="H35" s="24"/>
       <c r="I35" s="24"/>
     </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="36" spans="1:9" s="5" customFormat="1">
       <c r="A36" s="19"/>
       <c r="B36" s="19"/>
       <c r="C36" s="51"/>
@@ -2604,7 +2671,7 @@
       <c r="H36" s="24"/>
       <c r="I36" s="24"/>
     </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="37" spans="1:9" s="5" customFormat="1">
       <c r="A37" s="19"/>
       <c r="B37" s="19"/>
       <c r="C37" s="51"/>
@@ -2615,7 +2682,7 @@
       <c r="H37" s="24"/>
       <c r="I37" s="24"/>
     </row>
-    <row r="38" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="38" spans="1:9" s="5" customFormat="1">
       <c r="A38" s="19"/>
       <c r="B38" s="19"/>
       <c r="C38" s="51"/>
@@ -2625,7 +2692,7 @@
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
     </row>
-    <row r="39" spans="1:9" s="5" customFormat="1" ht="15">
+    <row r="39" spans="1:9" s="5" customFormat="1">
       <c r="A39" s="19"/>
       <c r="B39" s="19"/>
       <c r="C39" s="51"/>
@@ -2636,7 +2703,7 @@
       <c r="H39" s="24"/>
       <c r="I39" s="24"/>
     </row>
-    <row r="40" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="40" spans="1:9" s="4" customFormat="1">
       <c r="A40" s="19"/>
       <c r="B40" s="13"/>
       <c r="C40" s="51"/>
@@ -2646,7 +2713,7 @@
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="41" spans="1:9" s="4" customFormat="1">
       <c r="A41" s="19"/>
       <c r="B41" s="13"/>
       <c r="C41" s="51"/>
@@ -2656,7 +2723,7 @@
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="42" spans="1:9" s="4" customFormat="1">
       <c r="A42" s="19"/>
       <c r="B42" s="13"/>
       <c r="C42" s="51"/>
@@ -2666,7 +2733,7 @@
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
     </row>
-    <row r="43" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="43" spans="1:9" s="4" customFormat="1">
       <c r="A43" s="19"/>
       <c r="B43" s="13"/>
       <c r="C43" s="51"/>
@@ -2676,7 +2743,7 @@
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
     </row>
-    <row r="44" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="44" spans="1:9" s="4" customFormat="1">
       <c r="A44" s="19"/>
       <c r="B44" s="10"/>
       <c r="C44" s="51"/>
@@ -2686,7 +2753,7 @@
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
     </row>
-    <row r="45" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="45" spans="1:9" s="4" customFormat="1">
       <c r="A45" s="19"/>
       <c r="B45" s="13"/>
       <c r="C45" s="51"/>
@@ -2696,7 +2763,7 @@
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
     </row>
-    <row r="46" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="46" spans="1:9" s="4" customFormat="1">
       <c r="A46" s="13"/>
       <c r="B46" s="13"/>
       <c r="C46" s="51"/>
@@ -2706,7 +2773,7 @@
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
     </row>
-    <row r="47" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="47" spans="1:9" s="4" customFormat="1">
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="51"/>
@@ -2716,7 +2783,7 @@
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
     </row>
-    <row r="48" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="48" spans="1:9" s="4" customFormat="1">
       <c r="A48" s="13"/>
       <c r="B48" s="13"/>
       <c r="C48" s="51"/>
@@ -2726,7 +2793,7 @@
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
     </row>
-    <row r="49" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="49" spans="1:9" s="4" customFormat="1">
       <c r="A49" s="13"/>
       <c r="B49" s="13"/>
       <c r="C49" s="51"/>
@@ -2736,7 +2803,7 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
     </row>
-    <row r="50" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="50" spans="1:9" s="4" customFormat="1">
       <c r="A50" s="10"/>
       <c r="B50" s="13"/>
       <c r="C50" s="51"/>
@@ -2746,7 +2813,7 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
     </row>
-    <row r="51" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="51" spans="1:9" s="4" customFormat="1">
       <c r="A51" s="10"/>
       <c r="B51" s="13"/>
       <c r="C51" s="51"/>
@@ -2756,7 +2823,7 @@
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
     </row>
-    <row r="52" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="52" spans="1:9" s="4" customFormat="1">
       <c r="A52" s="10"/>
       <c r="B52" s="13"/>
       <c r="C52" s="51"/>
@@ -2767,7 +2834,7 @@
       <c r="H52" s="9"/>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="53" spans="1:9" s="4" customFormat="1">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="51"/>
@@ -2777,7 +2844,7 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
     </row>
-    <row r="54" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="54" spans="1:9" s="4" customFormat="1">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="51"/>
@@ -2787,7 +2854,7 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
     </row>
-    <row r="55" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="55" spans="1:9" s="4" customFormat="1">
       <c r="A55" s="13"/>
       <c r="B55" s="13"/>
       <c r="C55" s="51"/>
@@ -2797,7 +2864,7 @@
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
     </row>
-    <row r="56" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="56" spans="1:9" s="4" customFormat="1">
       <c r="A56" s="13"/>
       <c r="B56" s="13"/>
       <c r="C56" s="51"/>
@@ -2807,7 +2874,7 @@
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
     </row>
-    <row r="57" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="57" spans="1:9" s="4" customFormat="1">
       <c r="A57" s="13"/>
       <c r="B57" s="13"/>
       <c r="C57" s="51"/>
@@ -2817,7 +2884,7 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
     </row>
-    <row r="58" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="58" spans="1:9" s="4" customFormat="1">
       <c r="A58" s="13"/>
       <c r="B58" s="7"/>
       <c r="C58" s="52"/>
@@ -2827,7 +2894,7 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
     </row>
-    <row r="59" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="59" spans="1:9" s="4" customFormat="1">
       <c r="A59" s="13"/>
       <c r="B59" s="7"/>
       <c r="C59" s="52"/>
@@ -2837,7 +2904,7 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
     </row>
-    <row r="60" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="60" spans="1:9" s="4" customFormat="1">
       <c r="A60" s="13"/>
       <c r="B60" s="7"/>
       <c r="C60" s="52"/>
@@ -2847,7 +2914,7 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
     </row>
-    <row r="61" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="61" spans="1:9" s="4" customFormat="1">
       <c r="A61" s="13"/>
       <c r="B61" s="7"/>
       <c r="C61" s="52"/>
@@ -2857,7 +2924,7 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
     </row>
-    <row r="62" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="62" spans="1:9" s="4" customFormat="1">
       <c r="A62" s="13"/>
       <c r="B62" s="7"/>
       <c r="C62" s="52"/>
@@ -2867,7 +2934,7 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
     </row>
-    <row r="63" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="63" spans="1:9" s="4" customFormat="1">
       <c r="A63" s="13"/>
       <c r="B63" s="7"/>
       <c r="C63" s="52"/>
@@ -2878,7 +2945,7 @@
       <c r="H63" s="9"/>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="64" spans="1:9" s="4" customFormat="1">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="52"/>
@@ -2888,7 +2955,7 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
     </row>
-    <row r="65" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="65" spans="1:9" s="4" customFormat="1">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="52"/>
@@ -2899,7 +2966,7 @@
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="66" spans="1:9" s="4" customFormat="1">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="52"/>
@@ -2909,7 +2976,7 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
     </row>
-    <row r="67" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="67" spans="1:9" s="4" customFormat="1">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="52"/>
@@ -2919,7 +2986,7 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
     </row>
-    <row r="68" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="68" spans="1:9" s="4" customFormat="1">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="52"/>
@@ -2930,7 +2997,7 @@
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="69" spans="1:9" s="4" customFormat="1">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="52"/>
@@ -2940,7 +3007,7 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
     </row>
-    <row r="70" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="70" spans="1:9" s="4" customFormat="1">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="52"/>
@@ -2950,7 +3017,7 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
     </row>
-    <row r="71" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="71" spans="1:9" s="4" customFormat="1">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="52"/>
@@ -2960,7 +3027,7 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
     </row>
-    <row r="72" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="72" spans="1:9" s="4" customFormat="1">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="52"/>
@@ -2970,7 +3037,7 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
     </row>
-    <row r="73" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="73" spans="1:9" s="4" customFormat="1">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="52"/>
@@ -2980,7 +3047,7 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
     </row>
-    <row r="74" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="74" spans="1:9" s="4" customFormat="1">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="52"/>
@@ -2990,7 +3057,7 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
     </row>
-    <row r="75" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="75" spans="1:9" s="4" customFormat="1">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="52"/>
@@ -3001,7 +3068,7 @@
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="76" spans="1:9" s="4" customFormat="1">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="52"/>
@@ -3011,7 +3078,7 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
     </row>
-    <row r="77" spans="1:9" s="4" customFormat="1" ht="15">
+    <row r="77" spans="1:9" s="4" customFormat="1">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="52"/>
@@ -3531,7 +3598,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:9" ht="31.15">
+    <row r="3" spans="1:9" ht="30.95">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="82"/>
@@ -3550,7 +3617,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>4</v>
@@ -3571,7 +3638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A5" s="55">
         <v>45191</v>
       </c>
@@ -3579,10 +3646,10 @@
         <v>45191</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E5" s="6">
         <v>136</v>
@@ -3591,14 +3658,14 @@
         <v>45252</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A6" s="55">
         <v>45156</v>
       </c>
@@ -3606,26 +3673,26 @@
         <v>45156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A7" s="55">
         <v>45191</v>
       </c>
@@ -3633,10 +3700,10 @@
         <v>45153</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E7" s="38">
         <v>52</v>
@@ -3645,13 +3712,13 @@
         <v>45153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A8" s="55">
         <v>45156</v>
       </c>
@@ -3659,10 +3726,10 @@
         <v>45112</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E8" s="6">
         <v>211</v>
@@ -3671,16 +3738,16 @@
         <v>45138</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A9" s="40">
         <v>45153</v>
       </c>
@@ -3688,10 +3755,10 @@
         <v>45111</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E9" s="6">
         <v>249</v>
@@ -3700,16 +3767,16 @@
         <v>45138</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A10" s="55">
         <v>45112</v>
       </c>
@@ -3717,10 +3784,10 @@
         <v>42522</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E10" s="6">
         <v>169</v>
@@ -3729,16 +3796,16 @@
         <v>45086</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A11" s="55">
         <v>45107</v>
       </c>
@@ -3746,10 +3813,10 @@
         <v>44950</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E11" s="6">
         <v>75</v>
@@ -3758,16 +3825,16 @@
         <v>45010</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A12" s="55">
         <v>45063</v>
       </c>
@@ -3775,10 +3842,10 @@
         <v>44937</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E12" s="38">
         <v>81</v>
@@ -3787,14 +3854,14 @@
         <v>44990</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="13" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A13" s="57">
         <v>44949</v>
       </c>
@@ -3802,10 +3869,10 @@
         <v>44831</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E13" s="58">
         <v>1</v>
@@ -3814,14 +3881,14 @@
         <v>44890</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="14" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A14" s="40">
         <v>44930</v>
       </c>
@@ -3829,10 +3896,10 @@
         <v>44817</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E14" s="58">
         <v>77</v>
@@ -3841,14 +3908,14 @@
         <v>44880</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="15" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A15" s="22">
         <v>44827</v>
       </c>
@@ -3856,10 +3923,10 @@
         <v>44594</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E15" s="59">
         <v>198</v>
@@ -3868,13 +3935,13 @@
         <v>44659</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A16" s="22">
         <v>44817</v>
       </c>
@@ -3882,10 +3949,10 @@
         <v>44336</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E16" s="59">
         <v>94</v>
@@ -3894,16 +3961,16 @@
         <v>44394</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A17" s="22">
         <v>44595</v>
       </c>
@@ -3911,10 +3978,10 @@
         <v>44342</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E17" s="59">
         <v>464</v>
@@ -3923,13 +3990,13 @@
         <v>44403</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A18" s="22">
         <v>44334</v>
       </c>
@@ -3937,10 +4004,10 @@
         <v>44104</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E18" s="59">
         <v>13</v>
@@ -3949,13 +4016,13 @@
         <v>44104</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A19" s="22">
         <v>44342</v>
       </c>
@@ -3963,10 +4030,10 @@
         <v>44068</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E19" s="59">
         <v>40</v>
@@ -3975,13 +4042,13 @@
         <v>44061</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A20" s="22">
         <v>44105</v>
       </c>
@@ -3989,10 +4056,10 @@
         <v>44060</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E20" s="59">
         <v>106</v>
@@ -4001,13 +4068,13 @@
         <v>44057</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A21" s="22">
         <v>44064</v>
       </c>
@@ -4015,10 +4082,10 @@
         <v>44056</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E21" s="59">
         <v>272</v>
@@ -4027,16 +4094,16 @@
         <v>43914</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A22" s="22">
         <v>44057</v>
       </c>
@@ -4044,10 +4111,10 @@
         <v>44040</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E22" s="59">
         <v>1043</v>
@@ -4056,16 +4123,16 @@
         <v>44104</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A23" s="22">
         <v>44049</v>
       </c>
@@ -4073,10 +4140,10 @@
         <v>44040</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E23" s="59">
         <v>296</v>
@@ -4085,16 +4152,16 @@
         <v>44104</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A24" s="22">
         <v>44054</v>
       </c>
@@ -4102,10 +4169,10 @@
         <v>44042</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E24" s="59">
         <v>73</v>
@@ -4114,13 +4181,13 @@
         <v>44075</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A25" s="22">
         <v>44054</v>
       </c>
@@ -4128,10 +4195,10 @@
         <v>44022</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E25" s="59">
         <v>127</v>
@@ -4140,16 +4207,16 @@
         <v>44044</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A26" s="22">
         <v>44046</v>
       </c>
@@ -4157,10 +4224,10 @@
         <v>44004</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E26" s="59">
         <v>71</v>
@@ -4169,13 +4236,13 @@
         <v>43973</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A27" s="22">
         <v>44027</v>
       </c>
@@ -4183,10 +4250,10 @@
         <v>44012</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E27" s="59">
         <v>65</v>
@@ -4195,13 +4262,13 @@
         <v>44012</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A28" s="22">
         <v>44004</v>
       </c>
@@ -4209,10 +4276,10 @@
         <v>43985</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E28" s="59">
         <v>65</v>
@@ -4221,13 +4288,13 @@
         <v>43904</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A29" s="22">
         <v>44012</v>
       </c>
@@ -4235,10 +4302,10 @@
         <v>43980</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E29" s="59">
         <v>231</v>
@@ -4247,13 +4314,13 @@
         <v>43980</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A30" s="22">
         <v>43985</v>
       </c>
@@ -4261,10 +4328,10 @@
         <v>44068</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E30" s="59">
         <v>72</v>
@@ -4273,13 +4340,13 @@
         <v>43958</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A31" s="22">
         <v>43980</v>
       </c>
@@ -4287,10 +4354,10 @@
         <v>43948</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E31" s="59">
         <v>136</v>
@@ -4299,13 +4366,13 @@
         <v>43906</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A32" s="40">
         <v>44063</v>
       </c>
@@ -4313,10 +4380,10 @@
         <v>43942</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E32" s="59">
         <v>5</v>
@@ -4325,13 +4392,13 @@
         <v>43942</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A33" s="40">
         <v>43948</v>
       </c>
@@ -4339,10 +4406,10 @@
         <v>43944</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E33" s="59">
         <v>1</v>
@@ -4351,13 +4418,13 @@
         <v>43941</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A34" s="40">
         <v>43942</v>
       </c>
@@ -4365,10 +4432,10 @@
         <v>43938</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E34" s="59">
         <v>13</v>
@@ -4377,13 +4444,13 @@
         <v>43938</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A35" s="22">
         <v>43941</v>
       </c>
@@ -4391,10 +4458,10 @@
         <v>43935</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E35" s="59">
         <v>51</v>
@@ -4403,13 +4470,13 @@
         <v>43906</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A36" s="22">
         <v>43907</v>
       </c>
@@ -4417,10 +4484,10 @@
         <v>43925</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E36" s="59">
         <v>110</v>
@@ -4429,13 +4496,13 @@
         <v>43927</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A37" s="22">
         <v>43927</v>
       </c>
@@ -4443,10 +4510,10 @@
         <v>43917</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E37" s="59">
         <v>37</v>
@@ -4455,13 +4522,13 @@
         <v>43916</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A38" s="22">
         <v>43925</v>
       </c>
@@ -4469,10 +4536,10 @@
         <v>43913</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E38" s="59">
         <v>146</v>
@@ -4481,16 +4548,16 @@
         <v>43898</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A39" s="22">
         <v>43916</v>
       </c>
@@ -4498,10 +4565,10 @@
         <v>43910</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E39" s="59">
         <v>87</v>
@@ -4510,13 +4577,13 @@
         <v>43910</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A40" s="22">
         <v>43916</v>
       </c>
@@ -4524,10 +4591,10 @@
         <v>43913</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E40" s="59">
         <v>110</v>
@@ -4536,13 +4603,13 @@
         <v>43906</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A41" s="22">
         <v>43910</v>
       </c>
@@ -4550,10 +4617,10 @@
         <v>43510</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E41" s="59">
         <v>1</v>
@@ -4562,13 +4629,13 @@
         <v>43567</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A42" s="22">
         <v>43909</v>
       </c>
@@ -4576,25 +4643,25 @@
         <v>43486</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E42" s="59">
         <v>59</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A43" s="22">
         <v>43509</v>
       </c>
@@ -4602,10 +4669,10 @@
         <v>43479</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E43" s="59">
         <v>62</v>
@@ -4614,13 +4681,13 @@
         <v>43542</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A44" s="22">
         <v>43486</v>
       </c>
@@ -4628,10 +4695,10 @@
         <v>43413</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E44" s="59">
         <v>51</v>
@@ -4640,13 +4707,13 @@
         <v>43131</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A45" s="22">
         <v>43479</v>
       </c>
@@ -4654,10 +4721,10 @@
         <v>43405</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E45" s="59">
         <v>92</v>
@@ -4666,13 +4733,13 @@
         <v>43465</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A46" s="22">
         <v>43405</v>
       </c>
@@ -4680,10 +4747,10 @@
         <v>43405</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E46" s="59">
         <v>181</v>
@@ -4692,13 +4759,13 @@
         <v>43469</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A47" s="22">
         <v>76277</v>
       </c>
@@ -4706,10 +4773,10 @@
         <v>43382</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E47" s="59">
         <v>180</v>
@@ -4718,13 +4785,13 @@
         <v>43382</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A48" s="22">
         <v>76268</v>
       </c>
@@ -4732,10 +4799,10 @@
         <v>43363</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E48" s="59">
         <v>83</v>
@@ -4744,13 +4811,13 @@
         <v>43434</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A49" s="22">
         <v>43382</v>
       </c>
@@ -4758,10 +4825,10 @@
         <v>43276</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E49" s="59">
         <v>64</v>
@@ -4770,16 +4837,16 @@
         <v>43339</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A50" s="22">
         <v>43362</v>
       </c>
@@ -4787,10 +4854,10 @@
         <v>43252</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E50" s="59">
         <v>149</v>
@@ -4799,13 +4866,13 @@
         <v>43312</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A51" s="22">
         <v>43273</v>
       </c>
@@ -4813,10 +4880,10 @@
         <v>43042</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E51" s="59">
         <v>477</v>
@@ -4825,16 +4892,16 @@
         <v>43112</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A52" s="22">
         <v>43252</v>
       </c>
@@ -4842,25 +4909,25 @@
         <v>42990</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E52" s="59">
         <v>171</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A53" s="22">
         <v>43042</v>
       </c>
@@ -4868,10 +4935,10 @@
         <v>42496</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E53" s="59">
         <v>187</v>
@@ -4880,13 +4947,13 @@
         <v>42492</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A54" s="22">
         <v>42986</v>
       </c>
@@ -4894,10 +4961,10 @@
         <v>42495</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E54" s="59">
         <v>20</v>
@@ -4906,16 +4973,16 @@
         <v>42551</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A55" s="22">
         <v>42495</v>
       </c>
@@ -4923,10 +4990,10 @@
         <v>42468</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E55" s="59">
         <v>154</v>
@@ -4935,13 +5002,13 @@
         <v>42528</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A56" s="22">
         <v>42494</v>
       </c>
@@ -4949,25 +5016,25 @@
         <v>42401</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E56" s="59">
         <v>60</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A57" s="22">
         <v>42468</v>
       </c>
@@ -4975,10 +5042,10 @@
         <v>42384</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E57" s="59">
         <v>131</v>
@@ -4987,13 +5054,13 @@
         <v>42405</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A58" s="22">
         <v>42401</v>
       </c>
@@ -5001,25 +5068,25 @@
         <v>42326</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E58" s="59">
         <v>241</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A59" s="22">
         <v>42384</v>
       </c>
@@ -5027,25 +5094,25 @@
         <v>42320</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F59" s="59" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A60" s="22">
         <v>42326</v>
       </c>
@@ -5053,10 +5120,10 @@
         <v>42180</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E60" s="59">
         <v>70</v>
@@ -5065,13 +5132,13 @@
         <v>42240</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A61" s="22">
         <v>42318</v>
       </c>
@@ -5079,28 +5146,28 @@
         <v>42074</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E61" s="59" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F61" s="22">
         <v>42141</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A62" s="22">
         <v>42178</v>
       </c>
@@ -5108,25 +5175,25 @@
         <v>42065</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A63" s="22">
         <v>42069</v>
       </c>
@@ -5134,10 +5201,10 @@
         <v>41850</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E63" s="59">
         <v>5</v>
@@ -5146,13 +5213,13 @@
         <v>41912</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A64" s="22">
         <v>42062</v>
       </c>
@@ -5160,10 +5227,10 @@
         <v>41821</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E64" s="59">
         <v>142</v>
@@ -5172,13 +5239,13 @@
         <v>41882</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A65" s="22">
         <v>41850</v>
       </c>
@@ -5186,10 +5253,10 @@
         <v>41729</v>
       </c>
       <c r="C65" s="24" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E65" s="59">
         <v>115</v>
@@ -5198,16 +5265,16 @@
         <v>41774</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A66" s="22">
         <v>41820</v>
       </c>
@@ -5215,10 +5282,10 @@
         <v>41596</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E66" s="59">
         <v>49</v>
@@ -5227,13 +5294,13 @@
         <v>41654</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A67" s="22">
         <v>41724</v>
       </c>
@@ -5241,10 +5308,10 @@
         <v>41547</v>
       </c>
       <c r="C67" s="24" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D67" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E67" s="59">
         <v>1</v>
@@ -5253,13 +5320,13 @@
         <v>41608</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A68" s="22">
         <v>41593</v>
       </c>
@@ -5267,10 +5334,10 @@
         <v>41502</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E68" s="59">
         <v>66</v>
@@ -5279,13 +5346,13 @@
         <v>41555</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A69" s="22">
         <v>41547</v>
       </c>
@@ -5293,10 +5360,10 @@
         <v>41438</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E69" s="59">
         <v>3</v>
@@ -5305,13 +5372,13 @@
         <v>41425</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A70" s="22">
         <v>41495</v>
       </c>
@@ -5319,10 +5386,10 @@
         <v>41417</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E70" s="59">
         <v>62</v>
@@ -5331,13 +5398,13 @@
         <v>41485</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A71" s="22">
         <v>41425</v>
       </c>
@@ -5345,25 +5412,25 @@
         <v>41285</v>
       </c>
       <c r="C71" s="24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F71" s="22">
         <v>41347</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A72" s="22">
         <v>41416</v>
       </c>
@@ -5371,10 +5438,10 @@
         <v>41087</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E72" s="59">
         <v>51</v>
@@ -5383,13 +5450,13 @@
         <v>41148</v>
       </c>
       <c r="G72" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A73" s="22">
         <v>41285</v>
       </c>
@@ -5397,10 +5464,10 @@
         <v>41011</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E73" s="59">
         <v>150</v>
@@ -5409,16 +5476,16 @@
         <v>41071</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A74" s="22">
         <v>41087</v>
       </c>
@@ -5426,10 +5493,10 @@
         <v>40939</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E74" s="59">
         <v>70</v>
@@ -5438,16 +5505,16 @@
         <v>41000</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A75" s="22">
         <v>41011</v>
       </c>
@@ -5455,10 +5522,10 @@
         <v>40833</v>
       </c>
       <c r="C75" s="24" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E75" s="59">
         <v>110</v>
@@ -5467,14 +5534,14 @@
         <v>40833</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I75" s="24"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A76" s="22">
         <v>40938</v>
       </c>
@@ -5482,10 +5549,10 @@
         <v>40788</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E76" s="59">
         <v>16</v>
@@ -5494,14 +5561,14 @@
         <v>40846</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I76" s="24"/>
     </row>
-    <row r="77" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="77" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A77" s="22">
         <v>40833</v>
       </c>
@@ -5509,10 +5576,10 @@
         <v>40758</v>
       </c>
       <c r="C77" s="24" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E77" s="59">
         <v>9</v>
@@ -5521,14 +5588,14 @@
         <v>40816</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I77" s="24"/>
     </row>
-    <row r="78" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="78" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A78" s="22">
         <v>40785</v>
       </c>
@@ -5536,26 +5603,26 @@
         <v>40756</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E78" s="59">
         <v>98</v>
       </c>
       <c r="F78" s="59" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I78" s="24"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A79" s="22">
         <v>40752</v>
       </c>
@@ -5563,26 +5630,26 @@
         <v>40690</v>
       </c>
       <c r="C79" s="24" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E79" s="59">
         <v>21</v>
       </c>
       <c r="F79" s="59" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I79" s="24"/>
     </row>
-    <row r="80" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="80" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A80" s="22">
         <v>40753</v>
       </c>
@@ -5590,26 +5657,26 @@
         <v>40634</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E80" s="59">
         <v>98</v>
       </c>
       <c r="F80" s="59" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I80" s="24"/>
     </row>
-    <row r="81" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="81" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A81" s="22">
         <v>40688</v>
       </c>
@@ -5617,10 +5684,10 @@
         <v>40589</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E81" s="59">
         <v>5</v>
@@ -5629,14 +5696,14 @@
         <v>40644</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I81" s="24"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A82" s="22">
         <v>40634</v>
       </c>
@@ -5644,10 +5711,10 @@
         <v>40568</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E82" s="59">
         <v>122</v>
@@ -5656,14 +5723,14 @@
         <v>40592</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I82" s="24"/>
     </row>
-    <row r="83" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="83" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A83" s="22">
         <v>40589</v>
       </c>
@@ -5671,10 +5738,10 @@
         <v>40413</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E83" s="59">
         <v>89</v>
@@ -5683,14 +5750,14 @@
         <v>40452</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I83" s="24"/>
     </row>
-    <row r="84" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="84" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A84" s="22">
         <v>40565</v>
       </c>
@@ -5698,26 +5765,26 @@
         <v>40217</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D84" s="24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E84" s="59">
         <v>26</v>
       </c>
       <c r="F84" s="59" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I84" s="24"/>
     </row>
-    <row r="85" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="85" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A85" s="22">
         <v>40410</v>
       </c>
@@ -5725,10 +5792,10 @@
         <v>40217</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E85" s="59">
         <v>165</v>
@@ -5737,14 +5804,14 @@
         <v>40217</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I85" s="24"/>
     </row>
-    <row r="86" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="86" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A86" s="22">
         <v>40392</v>
       </c>
@@ -5752,10 +5819,10 @@
         <v>40182</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E86" s="59">
         <v>8</v>
@@ -5764,14 +5831,14 @@
         <v>40210</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I86" s="24"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A87" s="22">
         <v>40214</v>
       </c>
@@ -5779,26 +5846,26 @@
         <v>40141</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D87" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E87" s="59">
         <v>66</v>
       </c>
       <c r="F87" s="59" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I87" s="24"/>
     </row>
-    <row r="88" spans="1:9" s="5" customFormat="1" ht="13.9">
+    <row r="88" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A88" s="22">
         <v>40178</v>
       </c>
@@ -5806,28 +5873,28 @@
         <v>40141</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E88" s="59">
         <v>103</v>
       </c>
       <c r="F88" s="59" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A89" s="22">
         <v>40137</v>
       </c>
@@ -5835,25 +5902,25 @@
         <v>40094</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E89" s="59" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F89" s="22">
         <v>40147</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A90" s="22">
         <v>40137</v>
       </c>
@@ -5861,10 +5928,10 @@
         <v>40091</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E90" s="59">
         <v>63</v>
@@ -5873,13 +5940,13 @@
         <v>40148</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A91" s="22">
         <v>40094</v>
       </c>
@@ -5887,25 +5954,25 @@
         <v>40050</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E91" s="59" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F91" s="22">
         <v>39895</v>
       </c>
       <c r="G91" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A92" s="22">
         <v>40091</v>
       </c>
@@ -5913,10 +5980,10 @@
         <v>40008</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E92" s="59">
         <v>130</v>
@@ -5925,13 +5992,13 @@
         <v>39895</v>
       </c>
       <c r="G92" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A93" s="22">
         <v>40046</v>
       </c>
@@ -5939,10 +6006,10 @@
         <v>40008</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E93" s="59">
         <v>26</v>
@@ -5951,13 +6018,13 @@
         <v>40001</v>
       </c>
       <c r="G93" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A94" s="22">
         <v>40007</v>
       </c>
@@ -5965,10 +6032,10 @@
         <v>39895</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E94" s="59">
         <v>14</v>
@@ -5977,13 +6044,13 @@
         <v>39895</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A95" s="22">
         <v>40007</v>
       </c>
@@ -5991,10 +6058,10 @@
         <v>39996</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E95" s="59">
         <v>10</v>
@@ -6003,13 +6070,13 @@
         <v>40041</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="14.1">
       <c r="A96" s="22">
         <v>39995</v>
       </c>
@@ -6017,10 +6084,10 @@
         <v>39932</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E96" s="59">
         <v>171</v>
@@ -6029,16 +6096,16 @@
         <v>39994</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A97" s="22">
         <v>39980</v>
       </c>
@@ -6046,10 +6113,10 @@
         <v>39918</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E97" s="59">
         <v>55</v>
@@ -6058,13 +6125,13 @@
         <v>39994</v>
       </c>
       <c r="G97" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A98" s="22">
         <v>39931</v>
       </c>
@@ -6072,10 +6139,10 @@
         <v>39882</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D98" s="24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E98" s="59">
         <v>29</v>
@@ -6084,13 +6151,13 @@
         <v>39943</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A99" s="22">
         <v>39918</v>
       </c>
@@ -6098,10 +6165,10 @@
         <v>39881</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D99" s="24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E99" s="59">
         <v>71</v>
@@ -6110,13 +6177,13 @@
         <v>39941</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A100" s="22">
         <v>39883</v>
       </c>
@@ -6124,10 +6191,10 @@
         <v>39878</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D100" s="24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E100" s="59">
         <v>54</v>
@@ -6136,13 +6203,13 @@
         <v>39935</v>
       </c>
       <c r="G100" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A101" s="22">
         <v>39881</v>
       </c>
@@ -6150,10 +6217,10 @@
         <v>39877</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D101" s="24" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E101" s="59">
         <v>119</v>
@@ -6162,13 +6229,13 @@
         <v>39943</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A102" s="22">
         <v>39876</v>
       </c>
@@ -6176,10 +6243,10 @@
         <v>39864</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D102" s="24" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E102" s="59">
         <v>270</v>
@@ -6188,13 +6255,13 @@
         <v>39828</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" s="5" customFormat="1" ht="13.9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="5" customFormat="1" ht="14.1">
       <c r="A103" s="22">
         <v>39877</v>
       </c>
@@ -6202,10 +6269,10 @@
         <v>39825</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D103" s="24" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E103" s="59">
         <v>121</v>
@@ -6214,10 +6281,10 @@
         <v>39821</v>
       </c>
       <c r="G103" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H103" s="24" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:14">

--- a/data/states/ri/raw_download.xlsx
+++ b/data/states/ri/raw_download.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rigov.sharepoint.com/sites/DLT-WDS-Administrative-WARNNotice_RapidResponse/Shared Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E342F12-17AB-423F-9CD4-68EB2C988EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{BCB15270-1542-4A50-A931-4B910B345B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28017855-E323-4482-AB1F-E49EFBB423B0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{3D1EFEF8-FCA9-F542-BC18-3671B549873E}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="215">
   <si>
     <t>Rhode Island WARN Report</t>
   </si>
@@ -71,10 +71,604 @@
     <t>Union Address</t>
   </si>
   <si>
+    <t xml:space="preserve">Conduent </t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>1 (Remote worker)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideal US Talent Systems Worker OpCo LLC </t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9,891 Remote Workers (2 from RI)</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Allied Group, LLC</t>
+  </si>
+  <si>
+    <t>Cumberland, RI</t>
+  </si>
+  <si>
+    <t>5/25/26 - 6/6/26</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Northeast Transportation Services LLC</t>
+  </si>
+  <si>
+    <t>Pawtucket, RI</t>
+  </si>
+  <si>
+    <t>Teamsters Local 251, 121 Brightridge Avenue, East Providence, RI 02914</t>
+  </si>
+  <si>
+    <t>EaglePicher</t>
+  </si>
+  <si>
+    <t>East Greenwich</t>
+  </si>
+  <si>
+    <t>UNFI</t>
+  </si>
+  <si>
+    <t>Lincon</t>
+  </si>
+  <si>
+    <t>Hotel Viking</t>
+  </si>
+  <si>
+    <t>Newport</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Vertex Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Providence</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>CVS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woonsocket </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNFI </t>
+  </si>
+  <si>
+    <t>Gannett Publishing</t>
+  </si>
+  <si>
+    <t>Teamsters Local 251, 1201 Elmwood Ave., Prov., RI 02907( Paul Santos - President), Teamsters Local 3, Graphic Communications Conference, 1073 Hancock St., Suite 303, Quincy, MA 02169 ( Stephen Sullivan- President)</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>12/8/2024 through 12/21/2024</t>
+  </si>
+  <si>
+    <t>Kaleo</t>
+  </si>
+  <si>
+    <t>Riley Power Group</t>
+  </si>
+  <si>
+    <t>North Kingstown</t>
+  </si>
+  <si>
+    <t>11/22/24 (or within 14 days after)</t>
+  </si>
+  <si>
+    <t>10/21/24 (or within 14 days after)</t>
+  </si>
+  <si>
+    <t>Ennovi Advanced Mobility Solutions Rhode Island Inc</t>
+  </si>
+  <si>
+    <t>East Providence</t>
+  </si>
+  <si>
+    <t>Kirby Perkins Construction</t>
+  </si>
+  <si>
+    <t>Middletown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Claflin Company </t>
+  </si>
+  <si>
+    <t>Warwick</t>
+  </si>
+  <si>
+    <t>Rhode Island laborers' Local Union 1322 of the Laborers' International Union of North America, AFL-CIO, 410 South Main Street, Providence, RI 02903.</t>
+  </si>
+  <si>
+    <t>5/4/204</t>
+  </si>
+  <si>
+    <t>ASM GLOBAL</t>
+  </si>
+  <si>
+    <t>There are 8 Unions representing 800 workers. All 1,029 workers are being retained.</t>
+  </si>
+  <si>
+    <t>NMC</t>
+  </si>
+  <si>
+    <t>North Smithfield</t>
+  </si>
+  <si>
+    <t>5/2/24-7/1/24</t>
+  </si>
+  <si>
+    <t>UPS (updated from previous)</t>
+  </si>
+  <si>
+    <t>16 (additional)</t>
+  </si>
+  <si>
+    <t>Volta Inc</t>
+  </si>
+  <si>
+    <t>Woonsocket</t>
+  </si>
+  <si>
+    <t>Lakeside Book Company</t>
+  </si>
+  <si>
+    <t>Cumberland</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>Los Angeles Times Communications LLC</t>
+  </si>
+  <si>
+    <t>Company Name (* Denotes Covid 19 Related WARN)</t>
+  </si>
+  <si>
+    <t>Newport  Harbor Island Resort</t>
+  </si>
+  <si>
+    <t>CVS Health</t>
+  </si>
+  <si>
+    <t>Cumberland/Woonsocket</t>
+  </si>
+  <si>
+    <t>309 *updated 10/26/23</t>
+  </si>
+  <si>
+    <t>10/21/23 &amp; 12/30/23</t>
+  </si>
+  <si>
+    <t>TPI Composites Inc</t>
+  </si>
+  <si>
+    <t>Warren</t>
+  </si>
+  <si>
+    <t>Aramark Facility Services, LLC</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>226 South Main Street #2 Providence, RI 02903</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Providence</t>
+  </si>
+  <si>
+    <t>Sodexo, Inc and Affiliates</t>
+  </si>
+  <si>
+    <t>Smithfield</t>
+  </si>
+  <si>
+    <t>Local Union 1033, 410 S Main Street 3rd floor, Providence, RI 02906</t>
+  </si>
+  <si>
+    <t>Teamster Local Union 251 121 Brightridge Ave. East Providence, RI 02914</t>
+  </si>
+  <si>
+    <t>Monitronics International Inc (Brinks Home)</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>BayFirst Financial Corporation </t>
+  </si>
+  <si>
+    <t>Rubius Therapeutics</t>
+  </si>
+  <si>
+    <t>Santander</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>Pawtucket</t>
+  </si>
+  <si>
+    <t>Teamster Local Union 251, 121 Brightridge Ave., East Providence, RI 02914</t>
+  </si>
+  <si>
+    <t>Honeywell</t>
+  </si>
+  <si>
+    <t>Santander*</t>
+  </si>
+  <si>
+    <t>Hotel Viking*</t>
+  </si>
+  <si>
+    <t>Providence Mariott*</t>
+  </si>
+  <si>
+    <t>Omni Hotel &amp; Resorts*</t>
+  </si>
+  <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>Twin River - Lincoln*</t>
+  </si>
+  <si>
+    <t>Twin River - Tiverton*</t>
+  </si>
+  <si>
+    <t>RHD Rhode Island*</t>
+  </si>
+  <si>
+    <t>McLaughlin &amp; Moran, Inc*</t>
+  </si>
+  <si>
+    <t>Cranston</t>
+  </si>
+  <si>
+    <t>YMCA of Pawtucket *</t>
+  </si>
+  <si>
+    <t>Multiple Locations</t>
+  </si>
+  <si>
+    <t>Upserve *</t>
+  </si>
+  <si>
+    <t>Newport Marriot *</t>
+  </si>
+  <si>
+    <t>The Preservation Society of Newport County *</t>
+  </si>
+  <si>
+    <t>Bloomin Brands*</t>
+  </si>
+  <si>
+    <t>Warwick, Providence</t>
+  </si>
+  <si>
+    <t>Eastern Speciality/Check n GO*</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>CB Chadwick-BaRoss*</t>
+  </si>
+  <si>
+    <t>West Warwick</t>
+  </si>
+  <si>
+    <t>FGX Int*</t>
+  </si>
+  <si>
+    <t>Massage Envy*</t>
+  </si>
+  <si>
+    <t>Moo*</t>
+  </si>
+  <si>
+    <t>The Vanderbuilt*</t>
+  </si>
+  <si>
+    <t>Highgate*</t>
+  </si>
+  <si>
+    <t>Local 26 1010 Station Landing, 4th fl Medford Ma, 02155</t>
+  </si>
+  <si>
+    <t>Greystone*</t>
+  </si>
+  <si>
+    <t>HM Host*</t>
+  </si>
+  <si>
+    <t>Spectrum Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>Tuition Management Systems</t>
+  </si>
+  <si>
+    <t>4/1/2019,  8/30/2019</t>
+  </si>
+  <si>
+    <t>Agoda Travel Operations USA, Inc.</t>
+  </si>
+  <si>
+    <t>DAL Global Services, LLC (DGS)</t>
+  </si>
+  <si>
+    <t>Hooper Holmes, Inc. dba Provant Health</t>
+  </si>
+  <si>
+    <t>Nordstrom Providence Place</t>
+  </si>
+  <si>
+    <t>Matlet/Group</t>
+  </si>
+  <si>
+    <t>United Builders Supply Co., Inc.</t>
+  </si>
+  <si>
+    <t>Westerly</t>
+  </si>
+  <si>
+    <t>Chase Corp dba Neptco</t>
+  </si>
+  <si>
+    <t>IBEW Local 1499</t>
+  </si>
+  <si>
+    <t>Pinnacle Logistics</t>
+  </si>
+  <si>
+    <t>Memorial Hospital of Rhode Island</t>
+  </si>
+  <si>
+    <t>United Nurses and Allied Professionals Local 5082</t>
+  </si>
+  <si>
+    <t>Benny's</t>
+  </si>
+  <si>
+    <t>11/30/2017, 12/10/2017, and 12/31/2017</t>
+  </si>
+  <si>
+    <t>Homemade Real Foods</t>
+  </si>
+  <si>
+    <t>First Student</t>
+  </si>
+  <si>
+    <t>North Scituate</t>
+  </si>
+  <si>
+    <t>SEIU Local 1199</t>
+  </si>
+  <si>
+    <t>Aramark</t>
+  </si>
+  <si>
+    <t>Optum</t>
+  </si>
+  <si>
+    <t>4/01/16, 4/07/16</t>
+  </si>
+  <si>
+    <t>Sam's Club</t>
+  </si>
+  <si>
+    <t>Blue Cross Blue Shield of RI</t>
+  </si>
+  <si>
+    <t>1/04/16 through 8/2017</t>
+  </si>
+  <si>
+    <t>Fresenius Management Services, Inc.</t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>1/11/16 through 3/31/16</t>
+  </si>
+  <si>
+    <t>Teespring, Inc.</t>
+  </si>
+  <si>
+    <t>United Airlines, Inc.'s Airport Operations Division</t>
+  </si>
+  <si>
+    <t>54 Union 3 Non Union</t>
+  </si>
+  <si>
+    <t>International Assoc. of Machinists and Aerospace Workers, 1771 Commerce Drive, Suite 103 Elkgrove Village, IL 60007</t>
+  </si>
+  <si>
+    <t>190 company with an additional 100 contracted</t>
+  </si>
+  <si>
+    <t>6/2015 through 6/2016 5/2015 for contracted employees</t>
+  </si>
+  <si>
+    <t>IntegraMed Inc.</t>
+  </si>
+  <si>
+    <t>Providence and Middletown</t>
+  </si>
+  <si>
+    <t>Cox Communications</t>
+  </si>
+  <si>
+    <t>Sodexo</t>
+  </si>
+  <si>
+    <t>USAWR 90 Printery St. Providence</t>
+  </si>
+  <si>
+    <t>Money Management International</t>
+  </si>
+  <si>
+    <t>Dessert Services Inc.</t>
+  </si>
+  <si>
+    <t>Landauef Metropolitan, Inc.</t>
+  </si>
+  <si>
+    <t>Essential Salon Products Inc.</t>
+  </si>
+  <si>
+    <t>Sodexho Inc</t>
+  </si>
+  <si>
+    <t>American Suzuki Motor Corporation</t>
+  </si>
+  <si>
+    <t>Washington County</t>
+  </si>
+  <si>
+    <t>Portola Tech International Inc.</t>
+  </si>
+  <si>
+    <t>Pawtuxet Village Care &amp; Rehabilitation Center</t>
+  </si>
+  <si>
+    <t>North America AFL-CIO 410 South Main Street, Providence RI</t>
+  </si>
+  <si>
+    <t>John Crane, Inc.</t>
+  </si>
+  <si>
+    <t>Sealol Shop Union, 15 Pioneer Ave., Warwick RI 02888</t>
+  </si>
+  <si>
+    <t>Lowe?s Home Center</t>
+  </si>
+  <si>
+    <t>WSI</t>
+  </si>
+  <si>
+    <t>Lockheed Martin Corp - Global Training &amp; Logistics</t>
+  </si>
+  <si>
+    <t>BNY Mellon</t>
+  </si>
+  <si>
+    <t>10/28/2011, 11/10/2011</t>
+  </si>
+  <si>
+    <t>Flextronics Americas LLC</t>
+  </si>
+  <si>
+    <t>North Kingstown, Providence, Smithfield and Warwick</t>
+  </si>
+  <si>
+    <t>Staggered</t>
+  </si>
+  <si>
+    <t>Bank of New York Mellon (BNY Mellon)</t>
+  </si>
+  <si>
+    <t>6/6/11-10/30/11</t>
+  </si>
+  <si>
+    <t>Stanley Black &amp; Decker</t>
+  </si>
+  <si>
+    <t>Wal-Mart Stores, Inc. /Sam’s Club</t>
+  </si>
+  <si>
+    <t>Bank of America</t>
+  </si>
+  <si>
+    <t>Stanley Works Nail Dept.</t>
+  </si>
+  <si>
+    <t>10/1/2010-10/15/2010, 10/29/2010-11/12/2010, 12/3/2010-12/17/2010</t>
+  </si>
+  <si>
+    <t>The Ski Market</t>
+  </si>
+  <si>
+    <t>Leviton Mfg</t>
+  </si>
+  <si>
+    <t>1/20/10, 2/19/10</t>
+  </si>
+  <si>
+    <t>Liz Clayborne</t>
+  </si>
+  <si>
+    <t>4/19/10, 4/30/10</t>
+  </si>
+  <si>
+    <t>NE Joint Board, Local 324, UNITE HERE</t>
+  </si>
+  <si>
+    <t>60-80</t>
+  </si>
+  <si>
+    <t>A.T. Cross</t>
+  </si>
+  <si>
+    <t>additional 16</t>
+  </si>
+  <si>
+    <t>Portola</t>
+  </si>
+  <si>
+    <t>Victoria &amp; Company</t>
+  </si>
+  <si>
+    <t>HGA Quest</t>
+  </si>
+  <si>
+    <t>Nationwide - RI</t>
+  </si>
+  <si>
+    <t>Providence Public Library</t>
+  </si>
+  <si>
+    <t>United Service &amp; Allied Workers of RI 90 Printery St. Providence, RI 02904</t>
+  </si>
+  <si>
+    <t>Burrillville</t>
+  </si>
+  <si>
+    <t>APC by Schneider Electric</t>
+  </si>
+  <si>
+    <t>Colibri Group, Inc.</t>
+  </si>
+  <si>
+    <t>East Providence and Providence</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hasbro, Inc. </t>
-  </si>
-  <si>
-    <t>Pawtucket, RI</t>
   </si>
   <si>
     <r>
@@ -109,598 +703,13 @@
     </r>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conduent </t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>1 (Remote worker)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideal US Talent Systems Worker OpCo LLC </t>
-  </si>
-  <si>
-    <t>Minneapolis, MN</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 9,891 Remote Workers (2 from RI)</t>
-  </si>
-  <si>
-    <t>Allied Group, LLC</t>
-  </si>
-  <si>
-    <t>Cumberland, RI</t>
-  </si>
-  <si>
-    <t>5/25/26 - 6/6/26</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Northeast Transportation Services LLC</t>
-  </si>
-  <si>
-    <t>Teamsters Local 251, 121 Brightridge Avenue, East Providence, RI 02914</t>
-  </si>
-  <si>
-    <t>EaglePicher</t>
-  </si>
-  <si>
-    <t>East Greenwich</t>
-  </si>
-  <si>
-    <t>UNFI</t>
-  </si>
-  <si>
-    <t>Lincon</t>
-  </si>
-  <si>
-    <t>Hotel Viking</t>
-  </si>
-  <si>
-    <t>Newport</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Vertex Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Providence</t>
-  </si>
-  <si>
-    <t>Lincoln</t>
-  </si>
-  <si>
-    <t>CVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woonsocket </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNFI </t>
-  </si>
-  <si>
-    <t>Gannett Publishing</t>
-  </si>
-  <si>
-    <t>Teamsters Local 251, 1201 Elmwood Ave., Prov., RI 02907( Paul Santos - President), Teamsters Local 3, Graphic Communications Conference, 1073 Hancock St., Suite 303, Quincy, MA 02169 ( Stephen Sullivan- President)</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>12/8/2024 through 12/21/2024</t>
-  </si>
-  <si>
-    <t>Kaleo</t>
-  </si>
-  <si>
-    <t>Riley Power Group</t>
-  </si>
-  <si>
-    <t>North Kingstown</t>
-  </si>
-  <si>
-    <t>11/22/24 (or within 14 days after)</t>
-  </si>
-  <si>
-    <t>10/21/24 (or within 14 days after)</t>
-  </si>
-  <si>
-    <t>Ennovi Advanced Mobility Solutions Rhode Island Inc</t>
-  </si>
-  <si>
-    <t>East Providence</t>
-  </si>
-  <si>
-    <t>Kirby Perkins Construction</t>
-  </si>
-  <si>
-    <t>Middletown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Claflin Company </t>
-  </si>
-  <si>
-    <t>Warwick</t>
-  </si>
-  <si>
-    <t>Rhode Island laborers' Local Union 1322 of the Laborers' International Union of North America, AFL-CIO, 410 South Main Street, Providence, RI 02903.</t>
-  </si>
-  <si>
-    <t>5/4/204</t>
-  </si>
-  <si>
-    <t>ASM GLOBAL</t>
-  </si>
-  <si>
-    <t>There are 8 Unions representing 800 workers. All 1,029 workers are being retained.</t>
-  </si>
-  <si>
-    <t>NMC</t>
-  </si>
-  <si>
-    <t>North Smithfield</t>
-  </si>
-  <si>
-    <t>5/2/24-7/1/24</t>
-  </si>
-  <si>
-    <t>UPS (updated from previous)</t>
-  </si>
-  <si>
-    <t>16 (additional)</t>
-  </si>
-  <si>
-    <t>Volta Inc</t>
-  </si>
-  <si>
-    <t>Woonsocket</t>
-  </si>
-  <si>
-    <t>Lakeside Book Company</t>
-  </si>
-  <si>
-    <t>Cumberland</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>Los Angeles Times Communications LLC</t>
-  </si>
-  <si>
-    <t>Company Name (* Denotes Covid 19 Related WARN)</t>
-  </si>
-  <si>
-    <t>Newport  Harbor Island Resort</t>
-  </si>
-  <si>
-    <t>CVS Health</t>
-  </si>
-  <si>
-    <t>Cumberland/Woonsocket</t>
-  </si>
-  <si>
-    <t>309 *updated 10/26/23</t>
-  </si>
-  <si>
-    <t>10/21/23 &amp; 12/30/23</t>
-  </si>
-  <si>
-    <t>TPI Composites Inc</t>
-  </si>
-  <si>
-    <t>Warren</t>
-  </si>
-  <si>
-    <t>Aramark Facility Services, LLC</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>226 South Main Street #2 Providence, RI 02903</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Providence</t>
-  </si>
-  <si>
-    <t>Sodexo, Inc and Affiliates</t>
-  </si>
-  <si>
-    <t>Smithfield</t>
-  </si>
-  <si>
-    <t>Local Union 1033, 410 S Main Street 3rd floor, Providence, RI 02906</t>
-  </si>
-  <si>
-    <t>Teamster Local Union 251 121 Brightridge Ave. East Providence, RI 02914</t>
-  </si>
-  <si>
-    <t>Monitronics International Inc (Brinks Home)</t>
-  </si>
-  <si>
-    <t>Dallas, Texas</t>
-  </si>
-  <si>
-    <t>BayFirst Financial Corporation </t>
-  </si>
-  <si>
-    <t>Rubius Therapeutics</t>
-  </si>
-  <si>
-    <t>Santander</t>
-  </si>
-  <si>
-    <t>Angelica</t>
-  </si>
-  <si>
-    <t>Pawtucket</t>
-  </si>
-  <si>
-    <t>Teamster Local Union 251, 121 Brightridge Ave., East Providence, RI 02914</t>
-  </si>
-  <si>
-    <t>Honeywell</t>
-  </si>
-  <si>
-    <t>Santander*</t>
-  </si>
-  <si>
-    <t>Hotel Viking*</t>
-  </si>
-  <si>
-    <t>Providence Mariott*</t>
-  </si>
-  <si>
-    <t>Omni Hotel &amp; Resorts*</t>
-  </si>
-  <si>
-    <t>Multiple</t>
-  </si>
-  <si>
-    <t>Twin River - Lincoln*</t>
-  </si>
-  <si>
-    <t>Twin River - Tiverton*</t>
-  </si>
-  <si>
-    <t>RHD Rhode Island*</t>
-  </si>
-  <si>
-    <t>McLaughlin &amp; Moran, Inc*</t>
-  </si>
-  <si>
-    <t>Cranston</t>
-  </si>
-  <si>
-    <t>YMCA of Pawtucket *</t>
-  </si>
-  <si>
-    <t>Multiple Locations</t>
-  </si>
-  <si>
-    <t>Upserve *</t>
-  </si>
-  <si>
-    <t>Newport Marriot *</t>
-  </si>
-  <si>
-    <t>The Preservation Society of Newport County *</t>
-  </si>
-  <si>
-    <t>Bloomin Brands*</t>
-  </si>
-  <si>
-    <t>Warwick, Providence</t>
-  </si>
-  <si>
-    <t>Eastern Speciality/Check n GO*</t>
-  </si>
-  <si>
-    <t>RI</t>
-  </si>
-  <si>
-    <t>CB Chadwick-BaRoss*</t>
-  </si>
-  <si>
-    <t>West Warwick</t>
-  </si>
-  <si>
-    <t>FGX Int*</t>
-  </si>
-  <si>
-    <t>Massage Envy*</t>
-  </si>
-  <si>
-    <t>Moo*</t>
-  </si>
-  <si>
-    <t>The Vanderbuilt*</t>
-  </si>
-  <si>
-    <t>Highgate*</t>
-  </si>
-  <si>
-    <t>Local 26 1010 Station Landing, 4th fl Medford Ma, 02155</t>
-  </si>
-  <si>
-    <t>Greystone*</t>
-  </si>
-  <si>
-    <t>HM Host*</t>
-  </si>
-  <si>
-    <t>Spectrum Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Portsmouth</t>
-  </si>
-  <si>
-    <t>Tuition Management Systems</t>
-  </si>
-  <si>
-    <t>4/1/2019,  8/30/2019</t>
-  </si>
-  <si>
-    <t>Agoda Travel Operations USA, Inc.</t>
-  </si>
-  <si>
-    <t>DAL Global Services, LLC (DGS)</t>
-  </si>
-  <si>
-    <t>Hooper Holmes, Inc. dba Provant Health</t>
-  </si>
-  <si>
-    <t>Nordstrom Providence Place</t>
-  </si>
-  <si>
-    <t>Matlet/Group</t>
-  </si>
-  <si>
-    <t>United Builders Supply Co., Inc.</t>
-  </si>
-  <si>
-    <t>Westerly</t>
-  </si>
-  <si>
-    <t>Chase Corp dba Neptco</t>
-  </si>
-  <si>
-    <t>IBEW Local 1499</t>
-  </si>
-  <si>
-    <t>Pinnacle Logistics</t>
-  </si>
-  <si>
-    <t>Memorial Hospital of Rhode Island</t>
-  </si>
-  <si>
-    <t>United Nurses and Allied Professionals Local 5082</t>
-  </si>
-  <si>
-    <t>Benny's</t>
-  </si>
-  <si>
-    <t>11/30/2017, 12/10/2017, and 12/31/2017</t>
-  </si>
-  <si>
-    <t>Homemade Real Foods</t>
-  </si>
-  <si>
-    <t>First Student</t>
-  </si>
-  <si>
-    <t>North Scituate</t>
-  </si>
-  <si>
-    <t>SEIU Local 1199</t>
-  </si>
-  <si>
-    <t>Aramark</t>
-  </si>
-  <si>
-    <t>Optum</t>
-  </si>
-  <si>
-    <t>4/01/16, 4/07/16</t>
-  </si>
-  <si>
-    <t>Sam's Club</t>
-  </si>
-  <si>
-    <t>Blue Cross Blue Shield of RI</t>
-  </si>
-  <si>
-    <t>1/04/16 through 8/2017</t>
-  </si>
-  <si>
-    <t>Fresenius Management Services, Inc.</t>
-  </si>
-  <si>
-    <t>---</t>
-  </si>
-  <si>
-    <t>1/11/16 through 3/31/16</t>
-  </si>
-  <si>
-    <t>Teespring, Inc.</t>
-  </si>
-  <si>
-    <t>United Airlines, Inc.'s Airport Operations Division</t>
-  </si>
-  <si>
-    <t>54 Union 3 Non Union</t>
-  </si>
-  <si>
-    <t>International Assoc. of Machinists and Aerospace Workers, 1771 Commerce Drive, Suite 103 Elkgrove Village, IL 60007</t>
-  </si>
-  <si>
-    <t>190 company with an additional 100 contracted</t>
-  </si>
-  <si>
-    <t>6/2015 through 6/2016 5/2015 for contracted employees</t>
-  </si>
-  <si>
-    <t>IntegraMed Inc.</t>
-  </si>
-  <si>
-    <t>Providence and Middletown</t>
-  </si>
-  <si>
-    <t>Cox Communications</t>
-  </si>
-  <si>
-    <t>Sodexo</t>
-  </si>
-  <si>
-    <t>USAWR 90 Printery St. Providence</t>
-  </si>
-  <si>
-    <t>Money Management International</t>
-  </si>
-  <si>
-    <t>Dessert Services Inc.</t>
-  </si>
-  <si>
-    <t>Landauef Metropolitan, Inc.</t>
-  </si>
-  <si>
-    <t>Essential Salon Products Inc.</t>
-  </si>
-  <si>
-    <t>Sodexho Inc</t>
-  </si>
-  <si>
-    <t>American Suzuki Motor Corporation</t>
-  </si>
-  <si>
-    <t>Washington County</t>
-  </si>
-  <si>
-    <t>Portola Tech International Inc.</t>
-  </si>
-  <si>
-    <t>Pawtuxet Village Care &amp; Rehabilitation Center</t>
-  </si>
-  <si>
-    <t>North America AFL-CIO 410 South Main Street, Providence RI</t>
-  </si>
-  <si>
-    <t>John Crane, Inc.</t>
-  </si>
-  <si>
-    <t>Sealol Shop Union, 15 Pioneer Ave., Warwick RI 02888</t>
-  </si>
-  <si>
-    <t>Lowe?s Home Center</t>
-  </si>
-  <si>
-    <t>WSI</t>
-  </si>
-  <si>
-    <t>Lockheed Martin Corp - Global Training &amp; Logistics</t>
-  </si>
-  <si>
-    <t>BNY Mellon</t>
-  </si>
-  <si>
-    <t>10/28/2011, 11/10/2011</t>
-  </si>
-  <si>
-    <t>Flextronics Americas LLC</t>
-  </si>
-  <si>
-    <t>North Kingstown, Providence, Smithfield and Warwick</t>
-  </si>
-  <si>
-    <t>Staggered</t>
-  </si>
-  <si>
-    <t>Bank of New York Mellon (BNY Mellon)</t>
-  </si>
-  <si>
-    <t>6/6/11-10/30/11</t>
-  </si>
-  <si>
-    <t>Stanley Black &amp; Decker</t>
-  </si>
-  <si>
-    <t>Wal-Mart Stores, Inc. /Sam’s Club</t>
-  </si>
-  <si>
-    <t>Bank of America</t>
-  </si>
-  <si>
-    <t>Stanley Works Nail Dept.</t>
-  </si>
-  <si>
-    <t>10/1/2010-10/15/2010, 10/29/2010-11/12/2010, 12/3/2010-12/17/2010</t>
-  </si>
-  <si>
-    <t>The Ski Market</t>
-  </si>
-  <si>
-    <t>Leviton Mfg</t>
-  </si>
-  <si>
-    <t>1/20/10, 2/19/10</t>
-  </si>
-  <si>
-    <t>Liz Clayborne</t>
-  </si>
-  <si>
-    <t>4/19/10, 4/30/10</t>
-  </si>
-  <si>
-    <t>NE Joint Board, Local 324, UNITE HERE</t>
-  </si>
-  <si>
-    <t>60-80</t>
-  </si>
-  <si>
-    <t>A.T. Cross</t>
-  </si>
-  <si>
-    <t>additional 16</t>
-  </si>
-  <si>
-    <t>Portola</t>
-  </si>
-  <si>
-    <t>Victoria &amp; Company</t>
-  </si>
-  <si>
-    <t>HGA Quest</t>
-  </si>
-  <si>
-    <t>Nationwide - RI</t>
-  </si>
-  <si>
-    <t>Providence Public Library</t>
-  </si>
-  <si>
-    <t>United Service &amp; Allied Workers of RI 90 Printery St. Providence, RI 02904</t>
-  </si>
-  <si>
-    <t>Burrillville</t>
-  </si>
-  <si>
-    <t>APC by Schneider Electric</t>
-  </si>
-  <si>
-    <t>Colibri Group, Inc.</t>
-  </si>
-  <si>
-    <t>East Providence and Providence</t>
+    <t>Endeavors</t>
+  </si>
+  <si>
+    <t>3 RI-Based Employees</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
 </sst>
 </file>
@@ -1096,9 +1105,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1136,7 +1145,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1242,7 +1251,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1384,7 +1393,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1392,21 +1401,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0CB0631-2A55-452F-AC55-B4E9E0391533}">
-  <dimension ref="A1:R10"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="1" max="1" width="13.08203125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="4" max="4" width="21.58203125" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="15.58203125" customWidth="1"/>
     <col min="7" max="7" width="20.25" customWidth="1"/>
-    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
     <col min="9" max="9" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.6" customHeight="1">
+    <row r="1" spans="1:18" ht="15.5" customHeight="1">
       <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
@@ -1419,7 +1428,7 @@
       <c r="H1" s="83"/>
       <c r="I1" s="83"/>
     </row>
-    <row r="2" spans="1:18" ht="15.6" customHeight="1">
+    <row r="2" spans="1:18" ht="15.5" customHeight="1">
       <c r="A2" s="83"/>
       <c r="B2" s="83"/>
       <c r="C2" s="83"/>
@@ -1430,7 +1439,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:18" ht="30.95">
+    <row r="3" spans="1:18" ht="31">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="48"/>
@@ -1479,140 +1488,128 @@
       <c r="Q4"/>
       <c r="R4"/>
     </row>
-    <row r="5" spans="1:18" ht="30.95">
+    <row r="5" spans="1:18">
       <c r="A5" s="71">
+        <v>46324</v>
+      </c>
+      <c r="B5" s="71">
+        <v>46325</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="81" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="71">
+        <v>46387</v>
+      </c>
+      <c r="G5" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="79" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="31">
+      <c r="A6" s="71">
         <v>46303</v>
       </c>
-      <c r="B5" s="71">
+      <c r="B6" s="71">
         <v>46303</v>
       </c>
-      <c r="C5" s="80" t="s">
+      <c r="C6" s="80" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="81" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" s="71">
+        <v>46380</v>
+      </c>
+      <c r="G6" s="79" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="71">
+        <v>46199</v>
+      </c>
+      <c r="B7" s="71">
+        <v>46202</v>
+      </c>
+      <c r="C7" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="73" t="s">
+      <c r="D7" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E7" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="71">
-        <v>46380</v>
-      </c>
-      <c r="G5" s="79" t="s">
+      <c r="F7" s="71">
+        <v>46262</v>
+      </c>
+      <c r="H7" s="79"/>
+    </row>
+    <row r="8" spans="1:18" ht="31">
+      <c r="A8" s="71">
+        <v>46143</v>
+      </c>
+      <c r="B8" s="71">
+        <v>46147</v>
+      </c>
+      <c r="C8" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="79" t="s">
+      <c r="D8" s="73" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="71">
-        <v>46199</v>
-      </c>
-      <c r="B6" s="71">
-        <v>46202</v>
-      </c>
-      <c r="C6" s="80" t="s">
+      <c r="E8" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="81" t="s">
+      <c r="F8" s="71">
+        <v>46204</v>
+      </c>
+      <c r="H8" s="79" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="54" customFormat="1" ht="22.15" customHeight="1">
+      <c r="A9" s="71">
+        <v>46107</v>
+      </c>
+      <c r="B9" s="71">
+        <v>46112</v>
+      </c>
+      <c r="C9" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="71">
-        <v>46262</v>
-      </c>
-      <c r="H6" s="79"/>
-    </row>
-    <row r="7" spans="1:18" ht="30.95">
-      <c r="A7" s="71">
-        <v>46143</v>
-      </c>
-      <c r="B7" s="71">
-        <v>46147</v>
-      </c>
-      <c r="C7" s="80" t="s">
+      <c r="D9" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="73" t="s">
+      <c r="E9" s="79">
+        <v>154</v>
+      </c>
+      <c r="F9" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="71">
-        <v>46204</v>
-      </c>
-      <c r="H7" s="79" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" s="54" customFormat="1" ht="22.15" customHeight="1">
-      <c r="A8" s="71">
-        <v>46107</v>
-      </c>
-      <c r="B8" s="71">
-        <v>46112</v>
-      </c>
-      <c r="C8" s="72" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="79">
-        <v>154</v>
-      </c>
-      <c r="F8" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="79" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="79" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="72"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="73"/>
-      <c r="L8" s="73"/>
-      <c r="M8" s="73"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="73"/>
-      <c r="Q8" s="73"/>
-      <c r="R8" s="73"/>
-    </row>
-    <row r="9" spans="1:18" s="74" customFormat="1" ht="46.5">
-      <c r="A9" s="71">
-        <v>46100</v>
-      </c>
-      <c r="B9" s="71">
-        <v>46100</v>
-      </c>
-      <c r="C9" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="79">
-        <v>52</v>
-      </c>
-      <c r="F9" s="71">
-        <v>46151</v>
-      </c>
       <c r="G9" s="79" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H9" s="79" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="72" t="s">
-        <v>26</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="I9" s="72"/>
       <c r="J9" s="73"/>
       <c r="K9" s="73"/>
       <c r="L9" s="73"/>
@@ -1623,30 +1620,68 @@
       <c r="Q9" s="73"/>
       <c r="R9" s="73"/>
     </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="70">
+    <row r="10" spans="1:18" s="74" customFormat="1" ht="31">
+      <c r="A10" s="71">
+        <v>46100</v>
+      </c>
+      <c r="B10" s="71">
+        <v>46100</v>
+      </c>
+      <c r="C10" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="79">
+        <v>52</v>
+      </c>
+      <c r="F10" s="71">
+        <v>46151</v>
+      </c>
+      <c r="G10" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="70">
         <v>46035</v>
       </c>
-      <c r="B10" s="70">
+      <c r="B11" s="70">
         <v>46035</v>
       </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="28">
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="28">
         <v>38</v>
       </c>
-      <c r="F10" s="70">
+      <c r="F11" s="70">
         <v>46096</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>14</v>
+      <c r="G11" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1664,7 +1699,7 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
@@ -1759,10 +1794,10 @@
         <v>45910</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D5" s="63" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E5" s="62">
         <v>2</v>
@@ -1771,10 +1806,10 @@
         <v>45975</v>
       </c>
       <c r="G5" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="63"/>
       <c r="J5"/>
@@ -1796,10 +1831,10 @@
         <v>45903</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E6" s="62">
         <v>105</v>
@@ -1808,13 +1843,13 @@
         <v>45964</v>
       </c>
       <c r="G6" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="61" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -1827,7 +1862,7 @@
       <c r="R6"/>
       <c r="S6"/>
     </row>
-    <row r="7" spans="1:19" s="54" customFormat="1" ht="30.95">
+    <row r="7" spans="1:19" s="54" customFormat="1" ht="31">
       <c r="A7" s="63">
         <v>45814</v>
       </c>
@@ -1835,10 +1870,10 @@
         <v>45816</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E7" s="62">
         <v>125</v>
@@ -1847,10 +1882,10 @@
         <v>45874</v>
       </c>
       <c r="G7" s="62" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H7" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1872,10 +1907,10 @@
         <v>45736</v>
       </c>
       <c r="C8" s="61" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D8" s="61" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E8" s="62">
         <v>20</v>
@@ -1884,10 +1919,10 @@
         <v>45800</v>
       </c>
       <c r="G8" s="61" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H8" s="61" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1909,20 +1944,20 @@
         <v>45694</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E9" s="63"/>
       <c r="F9" s="63">
         <v>45815</v>
       </c>
       <c r="G9" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
@@ -1950,17 +1985,17 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:S123"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.08203125" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.58203125" customWidth="1"/>
     <col min="3" max="3" width="49.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="28.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.08203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="71.625" customWidth="1"/>
+    <col min="9" max="9" width="71.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1987,7 +2022,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:19" ht="30.95">
+    <row r="3" spans="1:19" ht="31">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="48"/>
@@ -2045,10 +2080,10 @@
         <v>45621</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E5" s="38">
         <v>796</v>
@@ -2057,10 +2092,10 @@
         <v>45682</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="38"/>
     </row>
@@ -2072,10 +2107,10 @@
         <v>45617</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E6" s="38">
         <v>121</v>
@@ -2084,10 +2119,10 @@
         <v>45681</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="39"/>
       <c r="J6" s="34"/>
@@ -2109,10 +2144,10 @@
         <v>45608</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E7" s="38">
         <v>136</v>
@@ -2121,13 +2156,13 @@
         <v>45726</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J7" s="34"/>
       <c r="K7" s="34"/>
@@ -2148,22 +2183,22 @@
         <v>45572</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E8" s="38">
         <v>632</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I8" s="34"/>
       <c r="J8" s="34"/>
@@ -2185,10 +2220,10 @@
         <v>45567</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E9" s="38">
         <v>1</v>
@@ -2197,7 +2232,7 @@
         <v>45626</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
@@ -2210,20 +2245,20 @@
         <v>45560</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" s="38">
         <v>13</v>
       </c>
       <c r="F10" s="40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G10" s="38"/>
       <c r="H10" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I10" s="38"/>
     </row>
@@ -2235,20 +2270,20 @@
         <v>45526</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E11" s="38">
         <v>117</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G11" s="38"/>
       <c r="H11" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I11" s="38"/>
     </row>
@@ -2260,10 +2295,10 @@
         <v>45504</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E12" s="38">
         <v>205</v>
@@ -2272,10 +2307,10 @@
         <v>45658</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" s="38"/>
     </row>
@@ -2287,10 +2322,10 @@
         <v>45485</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E13" s="38">
         <v>58</v>
@@ -2299,10 +2334,10 @@
         <v>45541</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="38"/>
     </row>
@@ -2314,10 +2349,10 @@
         <v>45432</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E14" s="38">
         <v>30</v>
@@ -2326,27 +2361,27 @@
         <v>45488</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="40" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B15" s="40">
         <v>45421</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E15" s="38">
         <v>1029</v>
@@ -2355,13 +2390,13 @@
         <v>45473</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2372,22 +2407,22 @@
         <v>45414</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E16" s="38">
         <v>36</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I16" s="38"/>
     </row>
@@ -2399,22 +2434,22 @@
         <v>45383</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F17" s="40">
         <v>45412</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I17" s="38"/>
     </row>
@@ -2426,10 +2461,10 @@
         <v>45383</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" s="38">
         <v>1</v>
@@ -2438,10 +2473,10 @@
         <v>45443</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H18" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I18" s="38"/>
     </row>
@@ -2453,10 +2488,10 @@
         <v>45349</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="38">
         <v>48</v>
@@ -2465,10 +2500,10 @@
         <v>45611</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I19" s="38"/>
     </row>
@@ -2480,10 +2515,10 @@
         <v>45328</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E20" s="38">
         <v>130</v>
@@ -2492,13 +2527,13 @@
         <v>45384</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="5" customFormat="1" ht="15" customHeight="1">
@@ -2509,10 +2544,10 @@
         <v>45316</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E21" s="38">
         <v>1</v>
@@ -2521,10 +2556,10 @@
         <v>45316</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I21" s="40"/>
     </row>
@@ -2542,7 +2577,7 @@
       <c r="E23" s="15"/>
       <c r="F23" s="42"/>
     </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="18.600000000000001" customHeight="1">
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="18.649999999999999" customHeight="1">
       <c r="B24" s="11"/>
       <c r="C24" s="49"/>
       <c r="D24" s="12"/>
@@ -3561,17 +3596,17 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:N177"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="60.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.58203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="103.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="103.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1">
@@ -3598,7 +3633,7 @@
       <c r="H2" s="83"/>
       <c r="I2" s="83"/>
     </row>
-    <row r="3" spans="1:9" ht="30.95">
+    <row r="3" spans="1:9" ht="31">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="82"/>
@@ -3617,7 +3652,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D4" s="35" t="s">
         <v>4</v>
@@ -3638,7 +3673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="5" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A5" s="55">
         <v>45191</v>
       </c>
@@ -3646,10 +3681,10 @@
         <v>45191</v>
       </c>
       <c r="C5" s="56" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E5" s="6">
         <v>136</v>
@@ -3658,14 +3693,14 @@
         <v>45252</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" s="17"/>
     </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="6" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A6" s="55">
         <v>45156</v>
       </c>
@@ -3673,26 +3708,26 @@
         <v>45156</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="40" t="s">
-        <v>75</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I6" s="17"/>
     </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="7" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A7" s="55">
         <v>45191</v>
       </c>
@@ -3700,10 +3735,10 @@
         <v>45153</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E7" s="38">
         <v>52</v>
@@ -3712,13 +3747,13 @@
         <v>45153</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A8" s="55">
         <v>45156</v>
       </c>
@@ -3726,10 +3761,10 @@
         <v>45112</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E8" s="6">
         <v>211</v>
@@ -3738,16 +3773,16 @@
         <v>45138</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A9" s="40">
         <v>45153</v>
       </c>
@@ -3755,10 +3790,10 @@
         <v>45111</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>81</v>
       </c>
       <c r="E9" s="6">
         <v>249</v>
@@ -3767,16 +3802,16 @@
         <v>45138</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A10" s="55">
         <v>45112</v>
       </c>
@@ -3784,10 +3819,10 @@
         <v>42522</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E10" s="6">
         <v>169</v>
@@ -3796,16 +3831,16 @@
         <v>45086</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A11" s="55">
         <v>45107</v>
       </c>
@@ -3813,10 +3848,10 @@
         <v>44950</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E11" s="6">
         <v>75</v>
@@ -3825,16 +3860,16 @@
         <v>45010</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A12" s="55">
         <v>45063</v>
       </c>
@@ -3842,10 +3877,10 @@
         <v>44937</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E12" s="38">
         <v>81</v>
@@ -3854,14 +3889,14 @@
         <v>44990</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I12" s="17"/>
     </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="13" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A13" s="57">
         <v>44949</v>
       </c>
@@ -3869,10 +3904,10 @@
         <v>44831</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E13" s="58">
         <v>1</v>
@@ -3881,14 +3916,14 @@
         <v>44890</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="14" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A14" s="40">
         <v>44930</v>
       </c>
@@ -3896,10 +3931,10 @@
         <v>44817</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E14" s="58">
         <v>77</v>
@@ -3908,14 +3943,14 @@
         <v>44880</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="15" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A15" s="22">
         <v>44827</v>
       </c>
@@ -3923,10 +3958,10 @@
         <v>44594</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" s="59">
         <v>198</v>
@@ -3935,13 +3970,13 @@
         <v>44659</v>
       </c>
       <c r="G15" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A16" s="22">
         <v>44817</v>
       </c>
@@ -3949,10 +3984,10 @@
         <v>44336</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E16" s="59">
         <v>94</v>
@@ -3961,16 +3996,16 @@
         <v>44394</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A17" s="22">
         <v>44595</v>
       </c>
@@ -3978,10 +4013,10 @@
         <v>44342</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E17" s="59">
         <v>464</v>
@@ -3990,13 +4025,13 @@
         <v>44403</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A18" s="22">
         <v>44334</v>
       </c>
@@ -4004,10 +4039,10 @@
         <v>44104</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E18" s="59">
         <v>13</v>
@@ -4016,13 +4051,13 @@
         <v>44104</v>
       </c>
       <c r="G18" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A19" s="22">
         <v>44342</v>
       </c>
@@ -4030,10 +4065,10 @@
         <v>44068</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E19" s="59">
         <v>40</v>
@@ -4042,13 +4077,13 @@
         <v>44061</v>
       </c>
       <c r="G19" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A20" s="22">
         <v>44105</v>
       </c>
@@ -4056,10 +4091,10 @@
         <v>44060</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E20" s="59">
         <v>106</v>
@@ -4068,13 +4103,13 @@
         <v>44057</v>
       </c>
       <c r="G20" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A21" s="22">
         <v>44064</v>
       </c>
@@ -4082,10 +4117,10 @@
         <v>44056</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E21" s="59">
         <v>272</v>
@@ -4094,16 +4129,16 @@
         <v>43914</v>
       </c>
       <c r="G21" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A22" s="22">
         <v>44057</v>
       </c>
@@ -4111,10 +4146,10 @@
         <v>44040</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E22" s="59">
         <v>1043</v>
@@ -4123,16 +4158,16 @@
         <v>44104</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A23" s="22">
         <v>44049</v>
       </c>
@@ -4140,10 +4175,10 @@
         <v>44040</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E23" s="59">
         <v>296</v>
@@ -4152,16 +4187,16 @@
         <v>44104</v>
       </c>
       <c r="G23" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A24" s="22">
         <v>44054</v>
       </c>
@@ -4169,10 +4204,10 @@
         <v>44042</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E24" s="59">
         <v>73</v>
@@ -4181,13 +4216,13 @@
         <v>44075</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A25" s="22">
         <v>44054</v>
       </c>
@@ -4195,10 +4230,10 @@
         <v>44022</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E25" s="59">
         <v>127</v>
@@ -4207,16 +4242,16 @@
         <v>44044</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A26" s="22">
         <v>44046</v>
       </c>
@@ -4224,10 +4259,10 @@
         <v>44004</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E26" s="59">
         <v>71</v>
@@ -4236,13 +4271,13 @@
         <v>43973</v>
       </c>
       <c r="G26" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A27" s="22">
         <v>44027</v>
       </c>
@@ -4250,10 +4285,10 @@
         <v>44012</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E27" s="59">
         <v>65</v>
@@ -4262,13 +4297,13 @@
         <v>44012</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A28" s="22">
         <v>44004</v>
       </c>
@@ -4276,10 +4311,10 @@
         <v>43985</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E28" s="59">
         <v>65</v>
@@ -4288,13 +4323,13 @@
         <v>43904</v>
       </c>
       <c r="G28" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A29" s="22">
         <v>44012</v>
       </c>
@@ -4302,10 +4337,10 @@
         <v>43980</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E29" s="59">
         <v>231</v>
@@ -4314,13 +4349,13 @@
         <v>43980</v>
       </c>
       <c r="G29" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A30" s="22">
         <v>43985</v>
       </c>
@@ -4328,10 +4363,10 @@
         <v>44068</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E30" s="59">
         <v>72</v>
@@ -4340,13 +4375,13 @@
         <v>43958</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A31" s="22">
         <v>43980</v>
       </c>
@@ -4354,10 +4389,10 @@
         <v>43948</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E31" s="59">
         <v>136</v>
@@ -4366,13 +4401,13 @@
         <v>43906</v>
       </c>
       <c r="G31" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A32" s="40">
         <v>44063</v>
       </c>
@@ -4380,10 +4415,10 @@
         <v>43942</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E32" s="59">
         <v>5</v>
@@ -4392,13 +4427,13 @@
         <v>43942</v>
       </c>
       <c r="G32" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A33" s="40">
         <v>43948</v>
       </c>
@@ -4406,10 +4441,10 @@
         <v>43944</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E33" s="59">
         <v>1</v>
@@ -4418,13 +4453,13 @@
         <v>43941</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A34" s="40">
         <v>43942</v>
       </c>
@@ -4432,10 +4467,10 @@
         <v>43938</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E34" s="59">
         <v>13</v>
@@ -4444,13 +4479,13 @@
         <v>43938</v>
       </c>
       <c r="G34" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A35" s="22">
         <v>43941</v>
       </c>
@@ -4458,10 +4493,10 @@
         <v>43935</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E35" s="59">
         <v>51</v>
@@ -4470,13 +4505,13 @@
         <v>43906</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A36" s="22">
         <v>43907</v>
       </c>
@@ -4484,10 +4519,10 @@
         <v>43925</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E36" s="59">
         <v>110</v>
@@ -4496,13 +4531,13 @@
         <v>43927</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A37" s="22">
         <v>43927</v>
       </c>
@@ -4510,10 +4545,10 @@
         <v>43917</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E37" s="59">
         <v>37</v>
@@ -4522,13 +4557,13 @@
         <v>43916</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A38" s="22">
         <v>43925</v>
       </c>
@@ -4536,10 +4571,10 @@
         <v>43913</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E38" s="59">
         <v>146</v>
@@ -4548,16 +4583,16 @@
         <v>43898</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A39" s="22">
         <v>43916</v>
       </c>
@@ -4565,10 +4600,10 @@
         <v>43910</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E39" s="59">
         <v>87</v>
@@ -4577,13 +4612,13 @@
         <v>43910</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A40" s="22">
         <v>43916</v>
       </c>
@@ -4591,10 +4626,10 @@
         <v>43913</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E40" s="59">
         <v>110</v>
@@ -4603,13 +4638,13 @@
         <v>43906</v>
       </c>
       <c r="G40" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A41" s="22">
         <v>43910</v>
       </c>
@@ -4617,10 +4652,10 @@
         <v>43510</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E41" s="59">
         <v>1</v>
@@ -4629,13 +4664,13 @@
         <v>43567</v>
       </c>
       <c r="G41" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A42" s="22">
         <v>43909</v>
       </c>
@@ -4643,25 +4678,25 @@
         <v>43486</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D42" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E42" s="59">
         <v>59</v>
       </c>
       <c r="F42" s="59" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G42" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H42" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A43" s="22">
         <v>43509</v>
       </c>
@@ -4669,10 +4704,10 @@
         <v>43479</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D43" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E43" s="59">
         <v>62</v>
@@ -4681,13 +4716,13 @@
         <v>43542</v>
       </c>
       <c r="G43" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A44" s="22">
         <v>43486</v>
       </c>
@@ -4695,10 +4730,10 @@
         <v>43413</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D44" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E44" s="59">
         <v>51</v>
@@ -4707,13 +4742,13 @@
         <v>43131</v>
       </c>
       <c r="G44" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A45" s="22">
         <v>43479</v>
       </c>
@@ -4721,10 +4756,10 @@
         <v>43405</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D45" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E45" s="59">
         <v>92</v>
@@ -4733,13 +4768,13 @@
         <v>43465</v>
       </c>
       <c r="G45" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A46" s="22">
         <v>43405</v>
       </c>
@@ -4747,10 +4782,10 @@
         <v>43405</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E46" s="59">
         <v>181</v>
@@ -4759,13 +4794,13 @@
         <v>43469</v>
       </c>
       <c r="G46" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H46" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A47" s="22">
         <v>76277</v>
       </c>
@@ -4773,10 +4808,10 @@
         <v>43382</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D47" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E47" s="59">
         <v>180</v>
@@ -4785,13 +4820,13 @@
         <v>43382</v>
       </c>
       <c r="G47" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A48" s="22">
         <v>76268</v>
       </c>
@@ -4799,10 +4834,10 @@
         <v>43363</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D48" s="24" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E48" s="59">
         <v>83</v>
@@ -4811,13 +4846,13 @@
         <v>43434</v>
       </c>
       <c r="G48" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A49" s="22">
         <v>43382</v>
       </c>
@@ -4825,10 +4860,10 @@
         <v>43276</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D49" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E49" s="59">
         <v>64</v>
@@ -4837,16 +4872,16 @@
         <v>43339</v>
       </c>
       <c r="G49" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A50" s="22">
         <v>43362</v>
       </c>
@@ -4854,10 +4889,10 @@
         <v>43252</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E50" s="59">
         <v>149</v>
@@ -4866,13 +4901,13 @@
         <v>43312</v>
       </c>
       <c r="G50" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A51" s="22">
         <v>43273</v>
       </c>
@@ -4880,10 +4915,10 @@
         <v>43042</v>
       </c>
       <c r="C51" s="24" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E51" s="59">
         <v>477</v>
@@ -4892,16 +4927,16 @@
         <v>43112</v>
       </c>
       <c r="G51" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A52" s="22">
         <v>43252</v>
       </c>
@@ -4909,25 +4944,25 @@
         <v>42990</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E52" s="59">
         <v>171</v>
       </c>
       <c r="F52" s="59" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A53" s="22">
         <v>43042</v>
       </c>
@@ -4935,10 +4970,10 @@
         <v>42496</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D53" s="24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E53" s="59">
         <v>187</v>
@@ -4947,13 +4982,13 @@
         <v>42492</v>
       </c>
       <c r="G53" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A54" s="22">
         <v>42986</v>
       </c>
@@ -4961,10 +4996,10 @@
         <v>42495</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E54" s="59">
         <v>20</v>
@@ -4973,16 +5008,16 @@
         <v>42551</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A55" s="22">
         <v>42495</v>
       </c>
@@ -4990,10 +5025,10 @@
         <v>42468</v>
       </c>
       <c r="C55" s="24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E55" s="59">
         <v>154</v>
@@ -5002,13 +5037,13 @@
         <v>42528</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A56" s="22">
         <v>42494</v>
       </c>
@@ -5016,25 +5051,25 @@
         <v>42401</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E56" s="59">
         <v>60</v>
       </c>
       <c r="F56" s="59" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H56" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A57" s="22">
         <v>42468</v>
       </c>
@@ -5042,10 +5077,10 @@
         <v>42384</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E57" s="59">
         <v>131</v>
@@ -5054,13 +5089,13 @@
         <v>42405</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A58" s="22">
         <v>42401</v>
       </c>
@@ -5068,25 +5103,25 @@
         <v>42326</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E58" s="59">
         <v>241</v>
       </c>
       <c r="F58" s="59" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A59" s="22">
         <v>42384</v>
       </c>
@@ -5094,25 +5129,25 @@
         <v>42320</v>
       </c>
       <c r="C59" s="24" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E59" s="59" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F59" s="59" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A60" s="22">
         <v>42326</v>
       </c>
@@ -5120,10 +5155,10 @@
         <v>42180</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E60" s="59">
         <v>70</v>
@@ -5132,13 +5167,13 @@
         <v>42240</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A61" s="22">
         <v>42318</v>
       </c>
@@ -5146,28 +5181,28 @@
         <v>42074</v>
       </c>
       <c r="C61" s="24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E61" s="59" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F61" s="22">
         <v>42141</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A62" s="22">
         <v>42178</v>
       </c>
@@ -5175,25 +5210,25 @@
         <v>42065</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E62" s="59" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F62" s="59" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A63" s="22">
         <v>42069</v>
       </c>
@@ -5201,10 +5236,10 @@
         <v>41850</v>
       </c>
       <c r="C63" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E63" s="59">
         <v>5</v>
@@ -5213,13 +5248,13 @@
         <v>41912</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A64" s="22">
         <v>42062</v>
       </c>
@@ -5227,10 +5262,10 @@
         <v>41821</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D64" s="24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E64" s="59">
         <v>142</v>
@@ -5239,13 +5274,13 @@
         <v>41882</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A65" s="22">
         <v>41850</v>
       </c>
@@ -5253,10 +5288,10 @@
         <v>41729</v>
       </c>
       <c r="C65" s="24" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E65" s="59">
         <v>115</v>
@@ -5265,16 +5300,16 @@
         <v>41774</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A66" s="22">
         <v>41820</v>
       </c>
@@ -5282,10 +5317,10 @@
         <v>41596</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D66" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E66" s="59">
         <v>49</v>
@@ -5294,13 +5329,13 @@
         <v>41654</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A67" s="22">
         <v>41724</v>
       </c>
@@ -5308,10 +5343,10 @@
         <v>41547</v>
       </c>
       <c r="C67" s="24" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D67" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E67" s="59">
         <v>1</v>
@@ -5320,13 +5355,13 @@
         <v>41608</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A68" s="22">
         <v>41593</v>
       </c>
@@ -5334,10 +5369,10 @@
         <v>41502</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D68" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E68" s="59">
         <v>66</v>
@@ -5346,13 +5381,13 @@
         <v>41555</v>
       </c>
       <c r="G68" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A69" s="22">
         <v>41547</v>
       </c>
@@ -5360,10 +5395,10 @@
         <v>41438</v>
       </c>
       <c r="C69" s="24" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E69" s="59">
         <v>3</v>
@@ -5372,13 +5407,13 @@
         <v>41425</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A70" s="22">
         <v>41495</v>
       </c>
@@ -5386,10 +5421,10 @@
         <v>41417</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E70" s="59">
         <v>62</v>
@@ -5398,13 +5433,13 @@
         <v>41485</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A71" s="22">
         <v>41425</v>
       </c>
@@ -5412,25 +5447,25 @@
         <v>41285</v>
       </c>
       <c r="C71" s="24" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E71" s="59" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F71" s="22">
         <v>41347</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A72" s="22">
         <v>41416</v>
       </c>
@@ -5438,10 +5473,10 @@
         <v>41087</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D72" s="24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E72" s="59">
         <v>51</v>
@@ -5450,13 +5485,13 @@
         <v>41148</v>
       </c>
       <c r="G72" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A73" s="22">
         <v>41285</v>
       </c>
@@ -5464,10 +5499,10 @@
         <v>41011</v>
       </c>
       <c r="C73" s="24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E73" s="59">
         <v>150</v>
@@ -5476,16 +5511,16 @@
         <v>41071</v>
       </c>
       <c r="G73" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I73" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A74" s="22">
         <v>41087</v>
       </c>
@@ -5493,10 +5528,10 @@
         <v>40939</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E74" s="59">
         <v>70</v>
@@ -5505,16 +5540,16 @@
         <v>41000</v>
       </c>
       <c r="G74" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I74" s="24" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A75" s="22">
         <v>41011</v>
       </c>
@@ -5522,10 +5557,10 @@
         <v>40833</v>
       </c>
       <c r="C75" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E75" s="59">
         <v>110</v>
@@ -5534,14 +5569,14 @@
         <v>40833</v>
       </c>
       <c r="G75" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I75" s="24"/>
     </row>
-    <row r="76" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="76" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A76" s="22">
         <v>40938</v>
       </c>
@@ -5549,10 +5584,10 @@
         <v>40788</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E76" s="59">
         <v>16</v>
@@ -5561,14 +5596,14 @@
         <v>40846</v>
       </c>
       <c r="G76" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I76" s="24"/>
     </row>
-    <row r="77" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="77" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A77" s="22">
         <v>40833</v>
       </c>
@@ -5576,10 +5611,10 @@
         <v>40758</v>
       </c>
       <c r="C77" s="24" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E77" s="59">
         <v>9</v>
@@ -5588,14 +5623,14 @@
         <v>40816</v>
       </c>
       <c r="G77" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I77" s="24"/>
     </row>
-    <row r="78" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="78" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A78" s="22">
         <v>40785</v>
       </c>
@@ -5603,26 +5638,26 @@
         <v>40756</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E78" s="59">
         <v>98</v>
       </c>
       <c r="F78" s="59" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G78" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I78" s="24"/>
     </row>
-    <row r="79" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="79" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A79" s="22">
         <v>40752</v>
       </c>
@@ -5630,26 +5665,26 @@
         <v>40690</v>
       </c>
       <c r="C79" s="24" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D79" s="24" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E79" s="59">
         <v>21</v>
       </c>
       <c r="F79" s="59" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I79" s="24"/>
     </row>
-    <row r="80" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="80" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A80" s="22">
         <v>40753</v>
       </c>
@@ -5657,26 +5692,26 @@
         <v>40634</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E80" s="59">
         <v>98</v>
       </c>
       <c r="F80" s="59" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I80" s="24"/>
     </row>
-    <row r="81" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="81" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A81" s="22">
         <v>40688</v>
       </c>
@@ -5684,10 +5719,10 @@
         <v>40589</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E81" s="59">
         <v>5</v>
@@ -5696,14 +5731,14 @@
         <v>40644</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I81" s="24"/>
     </row>
-    <row r="82" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="82" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A82" s="22">
         <v>40634</v>
       </c>
@@ -5711,10 +5746,10 @@
         <v>40568</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D82" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E82" s="59">
         <v>122</v>
@@ -5723,14 +5758,14 @@
         <v>40592</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I82" s="24"/>
     </row>
-    <row r="83" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="83" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A83" s="22">
         <v>40589</v>
       </c>
@@ -5738,10 +5773,10 @@
         <v>40413</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E83" s="59">
         <v>89</v>
@@ -5750,14 +5785,14 @@
         <v>40452</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I83" s="24"/>
     </row>
-    <row r="84" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="84" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A84" s="22">
         <v>40565</v>
       </c>
@@ -5765,26 +5800,26 @@
         <v>40217</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D84" s="24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E84" s="59">
         <v>26</v>
       </c>
       <c r="F84" s="59" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I84" s="24"/>
     </row>
-    <row r="85" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="85" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A85" s="22">
         <v>40410</v>
       </c>
@@ -5792,10 +5827,10 @@
         <v>40217</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E85" s="59">
         <v>165</v>
@@ -5804,14 +5839,14 @@
         <v>40217</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I85" s="24"/>
     </row>
-    <row r="86" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="86" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A86" s="22">
         <v>40392</v>
       </c>
@@ -5819,10 +5854,10 @@
         <v>40182</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E86" s="59">
         <v>8</v>
@@ -5831,14 +5866,14 @@
         <v>40210</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I86" s="24"/>
     </row>
-    <row r="87" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="87" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A87" s="22">
         <v>40214</v>
       </c>
@@ -5846,26 +5881,26 @@
         <v>40141</v>
       </c>
       <c r="C87" s="24" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D87" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E87" s="59">
         <v>66</v>
       </c>
       <c r="F87" s="59" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I87" s="24"/>
     </row>
-    <row r="88" spans="1:9" s="5" customFormat="1" ht="14.1">
+    <row r="88" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A88" s="22">
         <v>40178</v>
       </c>
@@ -5873,28 +5908,28 @@
         <v>40141</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D88" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E88" s="59">
         <v>103</v>
       </c>
       <c r="F88" s="59" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I88" s="24" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A89" s="22">
         <v>40137</v>
       </c>
@@ -5902,25 +5937,25 @@
         <v>40094</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D89" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E89" s="59" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F89" s="22">
         <v>40147</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A90" s="22">
         <v>40137</v>
       </c>
@@ -5928,10 +5963,10 @@
         <v>40091</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E90" s="59">
         <v>63</v>
@@ -5940,13 +5975,13 @@
         <v>40148</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A91" s="22">
         <v>40094</v>
       </c>
@@ -5954,25 +5989,25 @@
         <v>40050</v>
       </c>
       <c r="C91" s="24" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E91" s="59" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F91" s="22">
         <v>39895</v>
       </c>
       <c r="G91" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A92" s="22">
         <v>40091</v>
       </c>
@@ -5980,10 +6015,10 @@
         <v>40008</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E92" s="59">
         <v>130</v>
@@ -5992,13 +6027,13 @@
         <v>39895</v>
       </c>
       <c r="G92" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A93" s="22">
         <v>40046</v>
       </c>
@@ -6006,10 +6041,10 @@
         <v>40008</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E93" s="59">
         <v>26</v>
@@ -6018,13 +6053,13 @@
         <v>40001</v>
       </c>
       <c r="G93" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A94" s="22">
         <v>40007</v>
       </c>
@@ -6032,10 +6067,10 @@
         <v>39895</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E94" s="59">
         <v>14</v>
@@ -6044,13 +6079,13 @@
         <v>39895</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A95" s="22">
         <v>40007</v>
       </c>
@@ -6058,10 +6093,10 @@
         <v>39996</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E95" s="59">
         <v>10</v>
@@ -6070,13 +6105,13 @@
         <v>40041</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="5" customFormat="1" ht="14">
       <c r="A96" s="22">
         <v>39995</v>
       </c>
@@ -6084,10 +6119,10 @@
         <v>39932</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E96" s="59">
         <v>171</v>
@@ -6096,16 +6131,16 @@
         <v>39994</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A97" s="22">
         <v>39980</v>
       </c>
@@ -6113,10 +6148,10 @@
         <v>39918</v>
       </c>
       <c r="C97" s="24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E97" s="59">
         <v>55</v>
@@ -6125,13 +6160,13 @@
         <v>39994</v>
       </c>
       <c r="G97" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A98" s="22">
         <v>39931</v>
       </c>
@@ -6139,10 +6174,10 @@
         <v>39882</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D98" s="24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E98" s="59">
         <v>29</v>
@@ -6151,13 +6186,13 @@
         <v>39943</v>
       </c>
       <c r="G98" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A99" s="22">
         <v>39918</v>
       </c>
@@ -6165,10 +6200,10 @@
         <v>39881</v>
       </c>
       <c r="C99" s="24" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D99" s="24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E99" s="59">
         <v>71</v>
@@ -6177,13 +6212,13 @@
         <v>39941</v>
       </c>
       <c r="G99" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A100" s="22">
         <v>39883</v>
       </c>
@@ -6191,10 +6226,10 @@
         <v>39878</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D100" s="24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E100" s="59">
         <v>54</v>
@@ -6203,13 +6238,13 @@
         <v>39935</v>
       </c>
       <c r="G100" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A101" s="22">
         <v>39881</v>
       </c>
@@ -6217,10 +6252,10 @@
         <v>39877</v>
       </c>
       <c r="C101" s="24" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D101" s="24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E101" s="59">
         <v>119</v>
@@ -6229,13 +6264,13 @@
         <v>39943</v>
       </c>
       <c r="G101" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A102" s="22">
         <v>39876</v>
       </c>
@@ -6243,10 +6278,10 @@
         <v>39864</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D102" s="24" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E102" s="59">
         <v>270</v>
@@ -6255,13 +6290,13 @@
         <v>39828</v>
       </c>
       <c r="G102" s="24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H102" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" s="5" customFormat="1" ht="14.1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" s="5" customFormat="1" ht="14">
       <c r="A103" s="22">
         <v>39877</v>
       </c>
@@ -6269,10 +6304,10 @@
         <v>39825</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D103" s="24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E103" s="59">
         <v>121</v>
@@ -6281,10 +6316,10 @@
         <v>39821</v>
       </c>
       <c r="G103" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H103" s="24" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -7454,21 +7489,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D7CA4A7758DDF4F8A78677D3B22BD47" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f32e13009e9660c0d5c2c5b7ed8445ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e19eab3b-0a92-46fc-9552-a493c76cdc00" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8dceef0fefb3dead4f6c07070271e1f3" ns2:_="">
     <xsd:import namespace="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
@@ -7612,14 +7632,59 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0557A4BC-595F-498F-986F-63860A4E78D3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A410A84-27C1-4331-A67E-AC83C5FF1BE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BDC996-7CD8-43BD-838D-50E4C5CE2932}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="e19eab3b-0a92-46fc-9552-a493c76cdc00"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>